--- a/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.N_00219_18600707/oocihm.N_00219_18600707.2.xlsx
+++ b/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.N_00219_18600707/oocihm.N_00219_18600707.2.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="oocihm.N_00219_18600707.2" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="oocihm.N_00219_18600707.2" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -581,12 +581,12 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.N_00219_18600707\oocihm.N_00219_18600707.2.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.N_00219_18600707\oocihm.N_00219_18600707.2.txt</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.N_00219_18600707\oocihm.N_00219_18600707.2.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.N_00219_18600707\oocihm.N_00219_18600707.2.txt</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr"/>
@@ -991,7 +991,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.N_00219_18600707/oocihm.N_00219_18600707.2.xlsx
+++ b/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.N_00219_18600707/oocihm.N_00219_18600707.2.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="oocihm.N_00219_18600707.2" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="oocihm.N_00219_18600707.2" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -416,14 +416,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y228"/>
+  <dimension ref="A1:Y241"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="33" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="60" customWidth="1" min="6" max="6"/>
     <col width="60" customWidth="1" min="7" max="7"/>
     <col width="60" customWidth="1" min="8" max="8"/>
@@ -431,7 +431,7 @@
     <col width="60" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
     <col width="60" customWidth="1" min="14" max="14"/>
     <col width="60" customWidth="1" min="15" max="15"/>
     <col width="60" customWidth="1" min="16" max="16"/>
@@ -613,16 +613,20 @@
       </c>
       <c r="J2" s="1" t="inlineStr">
         <is>
-          <t>L5: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Merehantâ€™s Liquor Licence,</t>
+          <t>L74: stray/suspicious non-ASCII glyph(s): U+6E90 CJK UNIFIED IDEOGRAPH-6E90 | isolated marker/symbol line :: 源</t>
         </is>
       </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L1: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: ï»¿â€¢</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE, U+2022 BULLET | isolated marker/symbol line :: [BOM]•</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE, U+2022 BULLET | isolated marker/symbol line :: [BOM]•</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
           <t>L10: symbol-only separator/garbage line :: 383.25</t>
@@ -630,7 +634,7 @@
       </c>
       <c r="O2" s="1" t="inlineStr">
         <is>
-          <t>L139: isolated marker/symbol line :: E</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE, U+2022 BULLET | isolated marker/symbol line :: [BOM]•</t>
         </is>
       </c>
       <c r="P2" s="1" t="inlineStr">
@@ -646,7 +650,7 @@
       <c r="R2" s="1" t="inlineStr"/>
       <c r="S2" s="1" t="inlineStr">
         <is>
-          <t>L506: line starts with punctuation glued to text :: .centre of the Moons shadow in this</t>
+          <t>L3: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • en</t>
         </is>
       </c>
       <c r="T2" s="1" t="inlineStr">
@@ -681,7 +685,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>1043</t>
+          <t>729</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
@@ -704,12 +708,12 @@
       </c>
       <c r="J3" s="1" t="inlineStr">
         <is>
-          <t>L67: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: The Crops.â€” The Midge. â€” This</t>
+          <t>L78: stray/suspicious non-ASCII glyph(s): U+FF0C FULLWIDTH COMMA | suspicious token(s): 3ou (letter/digit mix) :: nal the 3ou. uit.， Samuel Woods.</t>
         </is>
       </c>
       <c r="K3" s="1" t="inlineStr">
         <is>
-          <t>L3: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢ en</t>
+          <t>L3: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • en</t>
         </is>
       </c>
       <c r="L3" s="1" t="inlineStr"/>
@@ -721,7 +725,7 @@
       </c>
       <c r="O3" s="1" t="inlineStr">
         <is>
-          <t>L221: symbol-only separator/garbage line :: 000-</t>
+          <t>L139: isolated marker/symbol line :: E</t>
         </is>
       </c>
       <c r="P3" s="1" t="inlineStr">
@@ -737,7 +741,7 @@
       <c r="R3" s="1" t="inlineStr"/>
       <c r="S3" s="1" t="inlineStr">
         <is>
-          <t>L856: line starts with lowercase prefix glued to capitalized word | suspicious token(s): aCoavia (odd internal casing) :: aCoavia him</t>
+          <t>L506: line starts with punctuation glued to text :: .centre of the Moons shadow in this</t>
         </is>
       </c>
       <c r="T3" s="1" t="inlineStr">
@@ -777,22 +781,22 @@
       <c r="G4" s="1" t="inlineStr"/>
       <c r="H4" s="1" t="inlineStr">
         <is>
-          <t>L78: suspicious token(s): 3ou (letter/digit mix) :: nal the 3ou. uit.ï¼Œ Samuel Woods.</t>
+          <t>L78: stray/suspicious non-ASCII glyph(s): U+FF0C FULLWIDTH COMMA | suspicious token(s): 3ou (letter/digit mix) :: nal the 3ou. uit.， Samuel Woods.</t>
         </is>
       </c>
       <c r="I4" s="1" t="inlineStr">
         <is>
-          <t>L745: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN | suspicious token(s): NewIPee (odd internal casing) :: General Walker Again.â€”The NewIPee like Lady Palmerstonâ€™s</t>
+          <t>L745: suspicious token(s): NewIPee (odd internal casing) :: General Walker Again.—The NewIPee like Lady Palmerston’s</t>
         </is>
       </c>
       <c r="J4" s="1" t="inlineStr">
         <is>
-          <t>L74: stray/suspicious non-ASCII glyph(s): U+FFFD REPLACEMENT CHARACTER :: æº�</t>
+          <t>L100: stray/suspicious non-ASCII glyph(s): U+798F CJK UNIFIED IDEOGRAPH-798F | isolated marker/symbol line :: 福</t>
         </is>
       </c>
       <c r="K4" s="1" t="inlineStr">
         <is>
-          <t>L17: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: was informed it had been left byâ€¢</t>
+          <t>L17: stray/suspicious non-ASCII glyph(s): U+2022 BULLET :: was informed it had been left by•</t>
         </is>
       </c>
       <c r="L4" s="1" t="inlineStr"/>
@@ -804,7 +808,7 @@
       </c>
       <c r="O4" s="1" t="inlineStr">
         <is>
-          <t>L225: symbol-only separator/garbage line :: 528,00</t>
+          <t>L221: symbol-only separator/garbage line :: 000-</t>
         </is>
       </c>
       <c r="P4" s="1" t="inlineStr">
@@ -820,7 +824,7 @@
       <c r="R4" s="1" t="inlineStr"/>
       <c r="S4" s="1" t="inlineStr">
         <is>
-          <t>L907: symbol-only separator/garbage line | punctuation artifact: double/multiple hyphen | line starts with punctuation glued to text :: ---------------_-</t>
+          <t>L856: line starts with lowercase prefix glued to capitalized word | suspicious token(s): aCoavia (odd internal casing) :: aCoavia him</t>
         </is>
       </c>
       <c r="T4" s="1" t="inlineStr"/>
@@ -842,12 +846,12 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>291</t>
+          <t>276</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>207</t>
+          <t>168</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr"/>
@@ -866,12 +870,12 @@
       </c>
       <c r="J5" s="1" t="inlineStr">
         <is>
-          <t>L91: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR :: so numerous ao so well authenticated. Paid to Ludger DEPA â€¦</t>
+          <t>L139: stray/suspicious non-ASCII glyph(s): U+798F CJK UNIFIED IDEOGRAPH-798F | isolated marker/symbol line :: 福</t>
         </is>
       </c>
       <c r="K5" s="1" t="inlineStr">
         <is>
-          <t>L27: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: of age and an American by birth.â€”</t>
+          <t>L124: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | punctuation artifact: repeated periods :: Tavern Licences,... •</t>
         </is>
       </c>
       <c r="L5" s="1" t="inlineStr"/>
@@ -883,7 +887,7 @@
       </c>
       <c r="O5" s="1" t="inlineStr">
         <is>
-          <t>L227: symbol-only separator/garbage line :: 3,50</t>
+          <t>L225: symbol-only separator/garbage line :: 528,00</t>
         </is>
       </c>
       <c r="P5" s="1" t="inlineStr">
@@ -899,7 +903,7 @@
       <c r="R5" s="1" t="inlineStr"/>
       <c r="S5" s="1" t="inlineStr">
         <is>
-          <t>L988: punctuation artifact: repeated periods | line starts with digit/letter garbage token | suspicious token(s): 2Deals (letter/digit mix), LaBarre (odd internal casing) | abbreviation/spacing may be garbled :: 2Deals to D.G. LaBarre Esq.... 2,56</t>
+          <t>L907: symbol-only separator/garbage line | punctuation artifact: double/multiple hyphen | line starts with punctuation glued to text :: ---------------_-</t>
         </is>
       </c>
       <c r="T5" s="1" t="inlineStr"/>
@@ -945,12 +949,12 @@
       </c>
       <c r="J6" s="1" t="inlineStr">
         <is>
-          <t>L100: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR, U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: ç¦�</t>
+          <t>L140: stray/suspicious non-ASCII glyph(s): U+65B0 CJK UNIFIED IDEOGRAPH-65B0 | isolated marker/symbol line :: 新</t>
         </is>
       </c>
       <c r="K6" s="1" t="inlineStr">
         <is>
-          <t>L38: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: form.â€”The annual meeting of the Abo-</t>
+          <t>L247: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L6" s="1" t="inlineStr"/>
@@ -962,7 +966,7 @@
       </c>
       <c r="O6" s="1" t="inlineStr">
         <is>
-          <t>L229: symbol-only separator/garbage line :: 60,00</t>
+          <t>L227: symbol-only separator/garbage line :: 3,50</t>
         </is>
       </c>
       <c r="P6" s="1" t="inlineStr">
@@ -976,7 +980,11 @@
         </is>
       </c>
       <c r="R6" s="1" t="inlineStr"/>
-      <c r="S6" s="1" t="inlineStr"/>
+      <c r="S6" s="1" t="inlineStr">
+        <is>
+          <t>L988: punctuation artifact: repeated periods | line starts with digit/letter garbage token | suspicious token(s): 2Deals (letter/digit mix), LaBarre (odd internal casing) | abbreviation/spacing may be garbled :: 2Deals to D.G. LaBarre Esq.... 2,56</t>
+        </is>
+      </c>
       <c r="T6" s="1" t="inlineStr"/>
       <c r="U6" s="1" t="inlineStr"/>
       <c r="V6" s="1" t="inlineStr"/>
@@ -1020,12 +1028,12 @@
       </c>
       <c r="J7" s="1" t="inlineStr">
         <is>
-          <t>L139: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR, U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: ç¦�</t>
+          <t>L144: stray/suspicious non-ASCII glyph(s): U+FF01 FULLWIDTH EXCLAMATION MARK | isolated marker/symbol line :: ！</t>
         </is>
       </c>
       <c r="K7" s="1" t="inlineStr">
         <is>
-          <t>L45: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: dians of Canada and Hudsonâ€™s Bay</t>
+          <t>L503: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | punctuation artifact: repeated periods :: should be in print in that city before it _• 000 ...</t>
         </is>
       </c>
       <c r="L7" s="1" t="inlineStr"/>
@@ -1037,7 +1045,7 @@
       </c>
       <c r="O7" s="1" t="inlineStr">
         <is>
-          <t>L231: symbol-only separator/garbage line :: 892,00</t>
+          <t>L229: symbol-only separator/garbage line :: 60,00</t>
         </is>
       </c>
       <c r="P7" s="1" t="inlineStr">
@@ -1091,12 +1099,12 @@
       </c>
       <c r="J8" s="1" t="inlineStr">
         <is>
-          <t>L144: stray/suspicious non-ASCII glyph(s): U+FFFD REPLACEMENT CHARACTER :: ï¼�</t>
+          <t>L156: stray/suspicious non-ASCII glyph(s): U+5BFF CJK UNIFIED IDEOGRAPH-5BFF | isolated marker/symbol line :: 寿</t>
         </is>
       </c>
       <c r="K8" s="1" t="inlineStr">
         <is>
-          <t>L70: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€” BOOK AND JOB PRINTING</t>
+          <t>L874: stray/suspicious non-ASCII glyph(s): U+2022 BULLET :: to turn the wilderness into • fruitful cess which he has acheived in establish I transferred to the Hondurean Govern</t>
         </is>
       </c>
       <c r="L8" s="1" t="inlineStr"/>
@@ -1108,13 +1116,13 @@
       </c>
       <c r="O8" s="1" t="inlineStr">
         <is>
-          <t>L247: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L231: symbol-only separator/garbage line :: 892,00</t>
         </is>
       </c>
       <c r="P8" s="1" t="inlineStr"/>
       <c r="Q8" s="1" t="inlineStr">
         <is>
-          <t>L112: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN | punctuation artifact: repeated periods :: 'Merchantâ€™s Liquor Licence,.... 512,0</t>
+          <t>L112: punctuation artifact: repeated periods :: 'Merchant’s Liquor Licence,.... 512,0</t>
         </is>
       </c>
       <c r="R8" s="1" t="inlineStr"/>
@@ -1158,12 +1166,12 @@
       </c>
       <c r="J9" s="1" t="inlineStr">
         <is>
-          <t>L156: stray/suspicious non-ASCII glyph(s): U+00AF MACRON | isolated marker/symbol line :: å¯¿</t>
+          <t>L158: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 。</t>
         </is>
       </c>
       <c r="K9" s="1" t="inlineStr">
         <is>
-          <t>L112: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN | punctuation artifact: repeated periods :: 'Merchantâ€™s Liquor Licence,.... 512,0</t>
+          <t>L956: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Maurice Sayer damage €</t>
         </is>
       </c>
       <c r="L9" s="1" t="inlineStr"/>
@@ -1175,7 +1183,7 @@
       </c>
       <c r="O9" s="1" t="inlineStr">
         <is>
-          <t>L336: isolated marker/symbol line :: 15</t>
+          <t>L247: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P9" s="1" t="inlineStr"/>
@@ -1201,12 +1209,12 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>39</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr"/>
@@ -1225,12 +1233,12 @@
       </c>
       <c r="J10" s="1" t="inlineStr">
         <is>
-          <t>L158: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: ã€‚</t>
+          <t>L175: stray/suspicious non-ASCII glyph(s): U+70B9 CJK UNIFIED IDEOGRAPH-70B9 | isolated marker/symbol line :: 点</t>
         </is>
       </c>
       <c r="K10" s="1" t="inlineStr">
         <is>
-          <t>L118: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN | punctuation artifact: repeated periods :: Pedlarâ€™s Licence, ...................13,00</t>
+          <t>L1009: stray/suspicious non-ASCII glyph(s): U+2022 BULLET :: are not it is true very rich, but they Party.•</t>
         </is>
       </c>
       <c r="L10" s="1" t="inlineStr"/>
@@ -1242,7 +1250,7 @@
       </c>
       <c r="O10" s="1" t="inlineStr">
         <is>
-          <t>L339: symbol-only separator/garbage line :: $6375,09</t>
+          <t>L336: isolated marker/symbol line :: 15</t>
         </is>
       </c>
       <c r="P10" s="1" t="inlineStr"/>
@@ -1273,7 +1281,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1287,19 +1295,15 @@
       </c>
       <c r="I11" s="1" t="inlineStr">
         <is>
-          <t>L878: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods | suspicious token(s): IEastern (odd internal casing) :: _A_____1:-n....______________________: â€”._...IEastern. The docks, says a curres- ment ceapelied a Sardinian merchant.</t>
+          <t>L878: punctuation artifact: repeated periods | suspicious token(s): IEastern (odd internal casing) :: _A_____1:-n....______________________: —._...IEastern. The docks, says a curres- ment ceapelied a Sardinian merchant.</t>
         </is>
       </c>
       <c r="J11" s="1" t="inlineStr">
         <is>
-          <t>L178: stray/suspicious non-ASCII glyph(s): U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: é‡�</t>
-        </is>
-      </c>
-      <c r="K11" s="1" t="inlineStr">
-        <is>
-          <t>L124: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | punctuation artifact: repeated periods :: Tavern Licences,... â€¢</t>
-        </is>
-      </c>
+          <t>L178: stray/suspicious non-ASCII glyph(s): U+91CD CJK UNIFIED IDEOGRAPH-91CD | isolated marker/symbol line :: 重</t>
+        </is>
+      </c>
+      <c r="K11" s="1" t="inlineStr"/>
       <c r="L11" s="1" t="inlineStr"/>
       <c r="M11" s="1" t="inlineStr"/>
       <c r="N11" s="1" t="inlineStr">
@@ -1309,13 +1313,13 @@
       </c>
       <c r="O11" s="1" t="inlineStr">
         <is>
-          <t>L358: isolated marker/symbol line :: 70</t>
+          <t>L339: symbol-only separator/garbage line :: $6375,09</t>
         </is>
       </c>
       <c r="P11" s="1" t="inlineStr"/>
       <c r="Q11" s="1" t="inlineStr">
         <is>
-          <t>L118: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN | punctuation artifact: repeated periods :: Pedlarâ€™s Licence, ...................13,00</t>
+          <t>L118: punctuation artifact: repeated periods :: Pedlar’s Licence, ...................13,00</t>
         </is>
       </c>
       <c r="R11" s="1" t="inlineStr"/>
@@ -1335,12 +1339,12 @@
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>227</t>
+          <t>240</t>
         </is>
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>82</t>
         </is>
       </c>
       <c r="D12" s="1" t="inlineStr"/>
@@ -1359,14 +1363,10 @@
       </c>
       <c r="J12" s="1" t="inlineStr">
         <is>
-          <t>L180: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR, U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: ç¦�</t>
-        </is>
-      </c>
-      <c r="K12" s="1" t="inlineStr">
-        <is>
-          <t>L151: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+02DC SMALL TILDE :: property â€˜</t>
-        </is>
-      </c>
+          <t>L180: stray/suspicious non-ASCII glyph(s): U+798F CJK UNIFIED IDEOGRAPH-798F | isolated marker/symbol line :: 福</t>
+        </is>
+      </c>
+      <c r="K12" s="1" t="inlineStr"/>
       <c r="L12" s="1" t="inlineStr"/>
       <c r="M12" s="1" t="inlineStr"/>
       <c r="N12" s="1" t="inlineStr">
@@ -1376,7 +1376,7 @@
       </c>
       <c r="O12" s="1" t="inlineStr">
         <is>
-          <t>L372: isolated marker/symbol line :: 10</t>
+          <t>L358: isolated marker/symbol line :: 70</t>
         </is>
       </c>
       <c r="P12" s="1" t="inlineStr"/>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C13" s="1" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>68</t>
         </is>
       </c>
       <c r="D13" s="1" t="inlineStr"/>
@@ -1421,19 +1421,15 @@
       </c>
       <c r="I13" s="1" t="inlineStr">
         <is>
-          <t>L895: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN | suspicious token(s): the28th (letter/digit mix) :: are concerned ; but it is the soil,â€” effect upon the base and slanderousingthe freedom of the Bay Islanders she wasnâ€™t Â°uch a big ship after all would commence on...</t>
+          <t>L895: suspicious token(s): the28th (letter/digit mix) :: are concerned ; but it is the soil,— effect upon the base and slanderousingthe freedom of the Bay Islanders she wasn’t °uch a big ship after all would commence on the2...</t>
         </is>
       </c>
       <c r="J13" s="1" t="inlineStr">
         <is>
-          <t>L243: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: The Solar 000-Eclipse.â€” The path of the</t>
-        </is>
-      </c>
-      <c r="K13" s="1" t="inlineStr">
-        <is>
-          <t>L180: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: known that there is a large tractâ€”al-</t>
-        </is>
-      </c>
+          <t>L192: stray/suspicious non-ASCII glyph(s): U+2192 RIGHTWARDS ARROW :: The Grave of Er.→ In the old grave</t>
+        </is>
+      </c>
+      <c r="K13" s="1" t="inlineStr"/>
       <c r="L13" s="1" t="inlineStr"/>
       <c r="M13" s="1" t="inlineStr"/>
       <c r="N13" s="1" t="inlineStr">
@@ -1443,7 +1439,7 @@
       </c>
       <c r="O13" s="1" t="inlineStr">
         <is>
-          <t>L385: symbol-only separator/garbage line :: 75.00</t>
+          <t>L372: isolated marker/symbol line :: 10</t>
         </is>
       </c>
       <c r="P13" s="1" t="inlineStr"/>
@@ -1474,7 +1470,7 @@
       </c>
       <c r="C14" s="1" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D14" s="1" t="inlineStr"/>
@@ -1488,35 +1484,31 @@
       </c>
       <c r="I14" s="1" t="inlineStr">
         <is>
-          <t>L904: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: double/multiple hyphen | suspicious token(s): 1arlin (letter/digit mix) :: ------------|following are the contents : â€” The child, from seven to ten years old, that Newcastle Station of the Grand Trunk Proceedings of the English 1arlin-</t>
+          <t>L904: punctuation artifact: double/multiple hyphen | suspicious token(s): 1arlin (letter/digit mix) :: ------------|following are the contents : — The child, from seven to ten years old, that Newcastle Station of the Grand Trunk Proceedings of the English 1arlin-</t>
         </is>
       </c>
       <c r="J14" s="1" t="inlineStr">
         <is>
-          <t>L245: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€” Boston Journal.</t>
-        </is>
-      </c>
-      <c r="K14" s="1" t="inlineStr">
-        <is>
-          <t>L216: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: The Steamship United States ground except under the regulationsâ€”that the</t>
-        </is>
-      </c>
+          <t>L292: stray/suspicious non-ASCII glyph(s): U+4E1A CJK UNIFIED IDEOGRAPH-4E1A | isolated marker/symbol line :: 业</t>
+        </is>
+      </c>
+      <c r="K14" s="1" t="inlineStr"/>
       <c r="L14" s="1" t="inlineStr"/>
       <c r="M14" s="1" t="inlineStr"/>
       <c r="N14" s="1" t="inlineStr">
         <is>
-          <t>L75: symbol-only separator/garbage line :: 637509</t>
+          <t>L74: stray/suspicious non-ASCII glyph(s): U+6E90 CJK UNIFIED IDEOGRAPH-6E90 | isolated marker/symbol line :: 源</t>
         </is>
       </c>
       <c r="O14" s="1" t="inlineStr">
         <is>
-          <t>L387: symbol-only separator/garbage line :: 18.69</t>
+          <t>L385: symbol-only separator/garbage line :: 75.00</t>
         </is>
       </c>
       <c r="P14" s="1" t="inlineStr"/>
       <c r="Q14" s="1" t="inlineStr">
         <is>
-          <t>L124: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | punctuation artifact: repeated periods :: Tavern Licences,... â€¢</t>
+          <t>L124: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | punctuation artifact: repeated periods :: Tavern Licences,... •</t>
         </is>
       </c>
       <c r="R14" s="1" t="inlineStr"/>
@@ -1560,24 +1552,20 @@
       </c>
       <c r="J15" s="1" t="inlineStr">
         <is>
-          <t>L292: stray/suspicious non-ASCII glyph(s): U+00B8 CEDILLA :: ä¸š</t>
-        </is>
-      </c>
-      <c r="K15" s="1" t="inlineStr">
-        <is>
-          <t>L236: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Hollowayâ€™s Pills.â€”There is no ha-</t>
-        </is>
-      </c>
+          <t>L318: stray/suspicious non-ASCII glyph(s): U+81EA CJK UNIFIED IDEOGRAPH-81EA | isolated marker/symbol line :: 自</t>
+        </is>
+      </c>
+      <c r="K15" s="1" t="inlineStr"/>
       <c r="L15" s="1" t="inlineStr"/>
       <c r="M15" s="1" t="inlineStr"/>
       <c r="N15" s="1" t="inlineStr">
         <is>
-          <t>L92: isolated marker/symbol line :: 30</t>
+          <t>L75: symbol-only separator/garbage line :: 637509</t>
         </is>
       </c>
       <c r="O15" s="1" t="inlineStr">
         <is>
-          <t>L389: symbol-only separator/garbage line :: 2.00</t>
+          <t>L387: symbol-only separator/garbage line :: 18.69</t>
         </is>
       </c>
       <c r="P15" s="1" t="inlineStr"/>
@@ -1617,30 +1605,26 @@
       <c r="G16" s="1" t="inlineStr"/>
       <c r="H16" s="1" t="inlineStr">
         <is>
-          <t>L933: suspicious token(s): 3ou (letter/digit mix) :: nal the 3ou. uit.ï¼Œ Samuel Woods.</t>
+          <t>L933: stray/suspicious non-ASCII glyph(s): U+FF0C FULLWIDTH COMMA | suspicious token(s): 3ou (letter/digit mix) :: nal the 3ou. uit.， Samuel Woods.</t>
         </is>
       </c>
       <c r="I16" s="1" t="inlineStr"/>
       <c r="J16" s="1" t="inlineStr">
         <is>
-          <t>L342: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Personal â€” A mpon is current in</t>
-        </is>
-      </c>
-      <c r="K16" s="1" t="inlineStr">
-        <is>
-          <t>L238: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Professor Hollowayâ€™s remediesin this</t>
-        </is>
-      </c>
+          <t>L525: stray/suspicious non-ASCII glyph(s): U+FF1B FULLWIDTH SEMICOLON :: Com easier Mixed 32 ； Yellow 32.</t>
+        </is>
+      </c>
+      <c r="K16" s="1" t="inlineStr"/>
       <c r="L16" s="1" t="inlineStr"/>
       <c r="M16" s="1" t="inlineStr"/>
       <c r="N16" s="1" t="inlineStr">
         <is>
-          <t>L100: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR, U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: ç¦�</t>
+          <t>L92: isolated marker/symbol line :: 30</t>
         </is>
       </c>
       <c r="O16" s="1" t="inlineStr">
         <is>
-          <t>L456: symbol-only separator/garbage line :: 10.00</t>
+          <t>L389: symbol-only separator/garbage line :: 2.00</t>
         </is>
       </c>
       <c r="P16" s="1" t="inlineStr"/>
@@ -1686,30 +1670,26 @@
       <c r="I17" s="1" t="inlineStr"/>
       <c r="J17" s="1" t="inlineStr">
         <is>
-          <t>L448: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Departure of the Japanese.â€” The</t>
-        </is>
-      </c>
-      <c r="K17" s="1" t="inlineStr">
-        <is>
-          <t>L247: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
-        </is>
-      </c>
+          <t>L737: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 。</t>
+        </is>
+      </c>
+      <c r="K17" s="1" t="inlineStr"/>
       <c r="L17" s="1" t="inlineStr"/>
       <c r="M17" s="1" t="inlineStr"/>
       <c r="N17" s="1" t="inlineStr">
         <is>
-          <t>L107: isolated marker/symbol line :: 70</t>
+          <t>L100: stray/suspicious non-ASCII glyph(s): U+798F CJK UNIFIED IDEOGRAPH-798F | isolated marker/symbol line :: 福</t>
         </is>
       </c>
       <c r="O17" s="1" t="inlineStr">
         <is>
-          <t>L458: isolated marker/symbol line :: 800</t>
+          <t>L456: symbol-only separator/garbage line :: 10.00</t>
         </is>
       </c>
       <c r="P17" s="1" t="inlineStr"/>
       <c r="Q17" s="1" t="inlineStr">
         <is>
-          <t>L353: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN | punctuation artifact: repeated periods :: rue. Esquireâ€™s barn, .....</t>
+          <t>L353: punctuation artifact: repeated periods :: rue. Esquire’s barn, .....</t>
         </is>
       </c>
       <c r="R17" s="1" t="inlineStr"/>
@@ -1737,24 +1717,20 @@
       <c r="I18" s="1" t="inlineStr"/>
       <c r="J18" s="1" t="inlineStr">
         <is>
-          <t>L451: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: perhaps $4.800 each â€” we suppose paid</t>
-        </is>
-      </c>
-      <c r="K18" s="1" t="inlineStr">
-        <is>
-          <t>L249: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Paid to AimÃ©</t>
-        </is>
-      </c>
+          <t>L819: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | isolated marker/symbol line :: ©</t>
+        </is>
+      </c>
+      <c r="K18" s="1" t="inlineStr"/>
       <c r="L18" s="1" t="inlineStr"/>
       <c r="M18" s="1" t="inlineStr"/>
       <c r="N18" s="1" t="inlineStr">
         <is>
-          <t>L125: symbol-only separator/garbage line :: 75.00</t>
+          <t>L107: isolated marker/symbol line :: 70</t>
         </is>
       </c>
       <c r="O18" s="1" t="inlineStr">
         <is>
-          <t>L460: symbol-only separator/garbage line :: 4.00</t>
+          <t>L458: isolated marker/symbol line :: 800</t>
         </is>
       </c>
       <c r="P18" s="1" t="inlineStr"/>
@@ -1788,24 +1764,20 @@
       <c r="I19" s="1" t="inlineStr"/>
       <c r="J19" s="1" t="inlineStr">
         <is>
-          <t>L506: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Liverpool, Jape 23.â€” Breadstuffs</t>
-        </is>
-      </c>
-      <c r="K19" s="1" t="inlineStr">
-        <is>
-          <t>L262: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: The Crops.â€” The Midge. â€” This</t>
-        </is>
-      </c>
+          <t>L842: stray/suspicious non-ASCII glyph(s): U+98DE CJK UNIFIED IDEOGRAPH-98DE | isolated marker/symbol line :: 飞</t>
+        </is>
+      </c>
+      <c r="K19" s="1" t="inlineStr"/>
       <c r="L19" s="1" t="inlineStr"/>
       <c r="M19" s="1" t="inlineStr"/>
       <c r="N19" s="1" t="inlineStr">
         <is>
-          <t>L133: symbol-only separator/garbage line :: 18.69</t>
+          <t>L125: symbol-only separator/garbage line :: 75.00</t>
         </is>
       </c>
       <c r="O19" s="1" t="inlineStr">
         <is>
-          <t>L462: symbol-only separator/garbage line :: 15.6)</t>
+          <t>L460: symbol-only separator/garbage line :: 4.00</t>
         </is>
       </c>
       <c r="P19" s="1" t="inlineStr"/>
@@ -1839,24 +1811,20 @@
       <c r="I20" s="1" t="inlineStr"/>
       <c r="J20" s="1" t="inlineStr">
         <is>
-          <t>L556: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Ashes quiet â€” Pots 276 61 to 29 3d;</t>
-        </is>
-      </c>
-      <c r="K20" s="1" t="inlineStr">
-        <is>
-          <t>L263: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: morning, says the St. Catherineâ€™s Jour-</t>
-        </is>
-      </c>
+          <t>L930: stray/suspicious non-ASCII glyph(s): U+6E90 CJK UNIFIED IDEOGRAPH-6E90 | isolated marker/symbol line :: 源</t>
+        </is>
+      </c>
+      <c r="K20" s="1" t="inlineStr"/>
       <c r="L20" s="1" t="inlineStr"/>
       <c r="M20" s="1" t="inlineStr"/>
       <c r="N20" s="1" t="inlineStr">
         <is>
-          <t>L139: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR, U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: ç¦�</t>
+          <t>L133: symbol-only separator/garbage line :: 18.69</t>
         </is>
       </c>
       <c r="O20" s="1" t="inlineStr">
         <is>
-          <t>L464: symbol-only separator/garbage line :: 8.00</t>
+          <t>L462: symbol-only separator/garbage line :: 15.6)</t>
         </is>
       </c>
       <c r="P20" s="1" t="inlineStr"/>
@@ -1890,24 +1858,20 @@
       <c r="I21" s="1" t="inlineStr"/>
       <c r="J21" s="1" t="inlineStr">
         <is>
-          <t>L573: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€” London Corres. N. O. Della.</t>
-        </is>
-      </c>
-      <c r="K21" s="1" t="inlineStr">
-        <is>
-          <t>L353: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN | punctuation artifact: repeated periods :: rue. Esquireâ€™s barn, .....</t>
-        </is>
-      </c>
+          <t>L933: stray/suspicious non-ASCII glyph(s): U+FF0C FULLWIDTH COMMA | suspicious token(s): 3ou (letter/digit mix) :: nal the 3ou. uit.， Samuel Woods.</t>
+        </is>
+      </c>
+      <c r="K21" s="1" t="inlineStr"/>
       <c r="L21" s="1" t="inlineStr"/>
       <c r="M21" s="1" t="inlineStr"/>
       <c r="N21" s="1" t="inlineStr">
         <is>
-          <t>L140: isolated marker/symbol line :: æ–°</t>
+          <t>L139: stray/suspicious non-ASCII glyph(s): U+798F CJK UNIFIED IDEOGRAPH-798F | isolated marker/symbol line :: 福</t>
         </is>
       </c>
       <c r="O21" s="1" t="inlineStr">
         <is>
-          <t>L466: symbol-only separator/garbage line :: 5.00</t>
+          <t>L464: symbol-only separator/garbage line :: 8.00</t>
         </is>
       </c>
       <c r="P21" s="1" t="inlineStr"/>
@@ -1941,24 +1905,20 @@
       <c r="I22" s="1" t="inlineStr"/>
       <c r="J22" s="1" t="inlineStr">
         <is>
-          <t>L621: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: world â€” a system of which any country</t>
-        </is>
-      </c>
-      <c r="K22" s="1" t="inlineStr">
-        <is>
-          <t>L412: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods; quote/punctuation debris :: tion No. Aâ€”.............</t>
-        </is>
-      </c>
+          <t>L943: stray/suspicious non-ASCII glyph(s): U+548C CJK UNIFIED IDEOGRAPH-548C | isolated marker/symbol line :: 和</t>
+        </is>
+      </c>
+      <c r="K22" s="1" t="inlineStr"/>
       <c r="L22" s="1" t="inlineStr"/>
       <c r="M22" s="1" t="inlineStr"/>
       <c r="N22" s="1" t="inlineStr">
         <is>
-          <t>L142: symbol-only separator/garbage line :: 1.00</t>
+          <t>L140: stray/suspicious non-ASCII glyph(s): U+65B0 CJK UNIFIED IDEOGRAPH-65B0 | isolated marker/symbol line :: 新</t>
         </is>
       </c>
       <c r="O22" s="1" t="inlineStr">
         <is>
-          <t>L468: symbol-only separator/garbage line :: 8.00</t>
+          <t>L466: symbol-only separator/garbage line :: 5.00</t>
         </is>
       </c>
       <c r="P22" s="1" t="inlineStr"/>
@@ -1992,30 +1952,26 @@
       <c r="I23" s="1" t="inlineStr"/>
       <c r="J23" s="1" t="inlineStr">
         <is>
-          <t>L721: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: about which there is no doubt â€” to</t>
-        </is>
-      </c>
-      <c r="K23" s="1" t="inlineStr">
-        <is>
-          <t>L480: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Tie Grave of Eve.â€”In the old grave-</t>
-        </is>
-      </c>
+          <t>L959: stray/suspicious non-ASCII glyph(s): U+798F CJK UNIFIED IDEOGRAPH-798F | isolated marker/symbol line :: 福</t>
+        </is>
+      </c>
+      <c r="K23" s="1" t="inlineStr"/>
       <c r="L23" s="1" t="inlineStr"/>
       <c r="M23" s="1" t="inlineStr"/>
       <c r="N23" s="1" t="inlineStr">
         <is>
-          <t>L156: stray/suspicious non-ASCII glyph(s): U+00AF MACRON | isolated marker/symbol line :: å¯¿</t>
+          <t>L142: symbol-only separator/garbage line :: 1.00</t>
         </is>
       </c>
       <c r="O23" s="1" t="inlineStr">
         <is>
-          <t>L470: isolated marker/symbol line :: 0</t>
+          <t>L468: symbol-only separator/garbage line :: 8.00</t>
         </is>
       </c>
       <c r="P23" s="1" t="inlineStr"/>
       <c r="Q23" s="1" t="inlineStr">
         <is>
-          <t>L412: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods; quote/punctuation debris :: tion No. Aâ€”.............</t>
+          <t>L412: punctuation artifact: repeated periods :: tion No. A—.............</t>
         </is>
       </c>
       <c r="R23" s="1" t="inlineStr"/>
@@ -2043,24 +1999,20 @@
       <c r="I24" s="1" t="inlineStr"/>
       <c r="J24" s="1" t="inlineStr">
         <is>
-          <t>L737: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: ã€‚</t>
-        </is>
-      </c>
-      <c r="K24" s="1" t="inlineStr">
-        <is>
-          <t>L483: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+02DC SMALL TILDE :: moss-covered tombstone containing theâ€˜</t>
-        </is>
-      </c>
+          <t>L999: stray/suspicious non-ASCII glyph(s): U+798F CJK UNIFIED IDEOGRAPH-798F | isolated marker/symbol line :: 福</t>
+        </is>
+      </c>
+      <c r="K24" s="1" t="inlineStr"/>
       <c r="L24" s="1" t="inlineStr"/>
       <c r="M24" s="1" t="inlineStr"/>
       <c r="N24" s="1" t="inlineStr">
         <is>
-          <t>L158: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: ã€‚</t>
+          <t>L144: stray/suspicious non-ASCII glyph(s): U+FF01 FULLWIDTH EXCLAMATION MARK | isolated marker/symbol line :: ！</t>
         </is>
       </c>
       <c r="O24" s="1" t="inlineStr">
         <is>
-          <t>L520: symbol-only separator/garbage line :: 4 00</t>
+          <t>L470: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="P24" s="1" t="inlineStr"/>
@@ -2094,24 +2046,20 @@
       <c r="I25" s="1" t="inlineStr"/>
       <c r="J25" s="1" t="inlineStr">
         <is>
-          <t>L819: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | isolated marker/symbol line :: Â©</t>
-        </is>
-      </c>
-      <c r="K25" s="1" t="inlineStr">
-        <is>
-          <t>L484: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: following inscription :â€”</t>
-        </is>
-      </c>
+          <t>L1000: stray/suspicious non-ASCII glyph(s): U+65B0 CJK UNIFIED IDEOGRAPH-65B0 | isolated marker/symbol line :: 新</t>
+        </is>
+      </c>
+      <c r="K25" s="1" t="inlineStr"/>
       <c r="L25" s="1" t="inlineStr"/>
       <c r="M25" s="1" t="inlineStr"/>
       <c r="N25" s="1" t="inlineStr">
         <is>
-          <t>L169: symbol-only separator/garbage line :: 10.00</t>
+          <t>L156: stray/suspicious non-ASCII glyph(s): U+5BFF CJK UNIFIED IDEOGRAPH-5BFF | isolated marker/symbol line :: 寿</t>
         </is>
       </c>
       <c r="O25" s="1" t="inlineStr">
         <is>
-          <t>L521: isolated marker/symbol line :: 18</t>
+          <t>L520: symbol-only separator/garbage line :: 4 00</t>
         </is>
       </c>
       <c r="P25" s="1" t="inlineStr"/>
@@ -2141,24 +2089,20 @@
       <c r="I26" s="1" t="inlineStr"/>
       <c r="J26" s="1" t="inlineStr">
         <is>
-          <t>L851: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Merehantâ€™s Liquor Licence,</t>
-        </is>
-      </c>
-      <c r="K26" s="1" t="inlineStr">
-        <is>
-          <t>L488: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER :: 28th, 1735, in ye 78th year of her age.â€�</t>
-        </is>
-      </c>
+          <t>L1004: stray/suspicious non-ASCII glyph(s): U+FF01 FULLWIDTH EXCLAMATION MARK | isolated marker/symbol line :: ！</t>
+        </is>
+      </c>
+      <c r="K26" s="1" t="inlineStr"/>
       <c r="L26" s="1" t="inlineStr"/>
       <c r="M26" s="1" t="inlineStr"/>
       <c r="N26" s="1" t="inlineStr">
         <is>
-          <t>L178: stray/suspicious non-ASCII glyph(s): U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: é‡�</t>
+          <t>L158: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 。</t>
         </is>
       </c>
       <c r="O26" s="1" t="inlineStr">
         <is>
-          <t>L523: symbol-only separator/garbage line :: 100.00</t>
+          <t>L521: isolated marker/symbol line :: 18</t>
         </is>
       </c>
       <c r="P26" s="1" t="inlineStr"/>
@@ -2188,24 +2132,20 @@
       <c r="I27" s="1" t="inlineStr"/>
       <c r="J27" s="1" t="inlineStr">
         <is>
-          <t>L921: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: The Crops.â€” The Midge. â€” This</t>
-        </is>
-      </c>
-      <c r="K27" s="1" t="inlineStr">
-        <is>
-          <t>L489: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€” Boston Journal.</t>
-        </is>
-      </c>
+          <t>L1016: stray/suspicious non-ASCII glyph(s): U+5BFF CJK UNIFIED IDEOGRAPH-5BFF | isolated marker/symbol line :: 寿</t>
+        </is>
+      </c>
+      <c r="K27" s="1" t="inlineStr"/>
       <c r="L27" s="1" t="inlineStr"/>
       <c r="M27" s="1" t="inlineStr"/>
       <c r="N27" s="1" t="inlineStr">
         <is>
-          <t>L179: isolated marker/symbol line :: 800</t>
+          <t>L169: symbol-only separator/garbage line :: 10.00</t>
         </is>
       </c>
       <c r="O27" s="1" t="inlineStr">
         <is>
-          <t>L539: symbol-only separator/garbage line :: 24.00</t>
+          <t>L523: symbol-only separator/garbage line :: 100.00</t>
         </is>
       </c>
       <c r="P27" s="1" t="inlineStr"/>
@@ -2235,24 +2175,20 @@
       <c r="I28" s="1" t="inlineStr"/>
       <c r="J28" s="1" t="inlineStr">
         <is>
-          <t>L930: stray/suspicious non-ASCII glyph(s): U+FFFD REPLACEMENT CHARACTER :: æº�</t>
-        </is>
-      </c>
-      <c r="K28" s="1" t="inlineStr">
-        <is>
-          <t>L503: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | punctuation artifact: repeated periods :: should be in print in that city before it _â€¢ 000 ...</t>
-        </is>
-      </c>
+          <t>L1018: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 。</t>
+        </is>
+      </c>
+      <c r="K28" s="1" t="inlineStr"/>
       <c r="L28" s="1" t="inlineStr"/>
       <c r="M28" s="1" t="inlineStr"/>
       <c r="N28" s="1" t="inlineStr">
         <is>
-          <t>L180: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR, U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: ç¦�</t>
+          <t>L175: stray/suspicious non-ASCII glyph(s): U+70B9 CJK UNIFIED IDEOGRAPH-70B9 | isolated marker/symbol line :: 点</t>
         </is>
       </c>
       <c r="O28" s="1" t="inlineStr">
         <is>
-          <t>L544: isolated marker/symbol line :: G.</t>
+          <t>L539: symbol-only separator/garbage line :: 24.00</t>
         </is>
       </c>
       <c r="P28" s="1" t="inlineStr"/>
@@ -2282,24 +2218,20 @@
       <c r="I29" s="1" t="inlineStr"/>
       <c r="J29" s="1" t="inlineStr">
         <is>
-          <t>L949: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR :: so numerous ao so well authenticated. Paid to Ludger DEPA â€¦</t>
-        </is>
-      </c>
-      <c r="K29" s="1" t="inlineStr">
-        <is>
-          <t>L505: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: can be received at Quebec or Montreal, The Solar Eclipse.â€”Thepath of the</t>
-        </is>
-      </c>
+          <t>L1035: stray/suspicious non-ASCII glyph(s): U+70B9 CJK UNIFIED IDEOGRAPH-70B9 | isolated marker/symbol line :: 点</t>
+        </is>
+      </c>
+      <c r="K29" s="1" t="inlineStr"/>
       <c r="L29" s="1" t="inlineStr"/>
       <c r="M29" s="1" t="inlineStr"/>
       <c r="N29" s="1" t="inlineStr">
         <is>
-          <t>L185: isolated marker/symbol line :: 0</t>
+          <t>L178: stray/suspicious non-ASCII glyph(s): U+91CD CJK UNIFIED IDEOGRAPH-91CD | isolated marker/symbol line :: 重</t>
         </is>
       </c>
       <c r="O29" s="1" t="inlineStr">
         <is>
-          <t>L560: isolated marker/symbol line :: 50</t>
+          <t>L544: isolated marker/symbol line :: G.</t>
         </is>
       </c>
       <c r="P29" s="1" t="inlineStr"/>
@@ -2329,24 +2261,20 @@
       <c r="I30" s="1" t="inlineStr"/>
       <c r="J30" s="1" t="inlineStr">
         <is>
-          <t>L959: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR, U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: ç¦�</t>
-        </is>
-      </c>
-      <c r="K30" s="1" t="inlineStr">
-        <is>
-          <t>L514: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: double/multiple hyphen :: setting limits to - : --= -----frhis â€” -</t>
-        </is>
-      </c>
+          <t>L1038: stray/suspicious non-ASCII glyph(s): U+91CD CJK UNIFIED IDEOGRAPH-91CD | isolated marker/symbol line :: 重</t>
+        </is>
+      </c>
+      <c r="K30" s="1" t="inlineStr"/>
       <c r="L30" s="1" t="inlineStr"/>
       <c r="M30" s="1" t="inlineStr"/>
       <c r="N30" s="1" t="inlineStr">
         <is>
-          <t>L187: isolated marker/symbol line :: 400</t>
+          <t>L179: isolated marker/symbol line :: 800</t>
         </is>
       </c>
       <c r="O30" s="1" t="inlineStr">
         <is>
-          <t>L562: symbol-only separator/garbage line :: 4.05</t>
+          <t>L560: isolated marker/symbol line :: 50</t>
         </is>
       </c>
       <c r="P30" s="1" t="inlineStr"/>
@@ -2376,30 +2304,26 @@
       <c r="I31" s="1" t="inlineStr"/>
       <c r="J31" s="1" t="inlineStr">
         <is>
-          <t>L999: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR, U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: ç¦�</t>
-        </is>
-      </c>
-      <c r="K31" s="1" t="inlineStr">
-        <is>
-          <t>L555: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€œtotal darkness" at the above place</t>
-        </is>
-      </c>
+          <t>L1040: stray/suspicious non-ASCII glyph(s): U+798F CJK UNIFIED IDEOGRAPH-798F | isolated marker/symbol line :: 福</t>
+        </is>
+      </c>
+      <c r="K31" s="1" t="inlineStr"/>
       <c r="L31" s="1" t="inlineStr"/>
       <c r="M31" s="1" t="inlineStr"/>
       <c r="N31" s="1" t="inlineStr">
         <is>
-          <t>L198: isolated marker/symbol line :: .</t>
+          <t>L180: stray/suspicious non-ASCII glyph(s): U+798F CJK UNIFIED IDEOGRAPH-798F | isolated marker/symbol line :: 福</t>
         </is>
       </c>
       <c r="O31" s="1" t="inlineStr">
         <is>
-          <t>L566: isolated marker/symbol line :: J.</t>
+          <t>L562: symbol-only separator/garbage line :: 4.05</t>
         </is>
       </c>
       <c r="P31" s="1" t="inlineStr"/>
       <c r="Q31" s="1" t="inlineStr">
         <is>
-          <t>L503: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | punctuation artifact: repeated periods :: should be in print in that city before it _â€¢ 000 ...</t>
+          <t>L503: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | punctuation artifact: repeated periods :: should be in print in that city before it _• 000 ...</t>
         </is>
       </c>
       <c r="R31" s="1" t="inlineStr"/>
@@ -2423,30 +2347,26 @@
       <c r="I32" s="1" t="inlineStr"/>
       <c r="J32" s="1" t="inlineStr">
         <is>
-          <t>L1004: stray/suspicious non-ASCII glyph(s): U+FFFD REPLACEMENT CHARACTER :: ï¼�</t>
-        </is>
-      </c>
-      <c r="K32" s="1" t="inlineStr">
-        <is>
-          <t>L557: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: the Moonâ€™s shadow, 100 miles or 50 to</t>
-        </is>
-      </c>
+          <t>L1052: stray/suspicious non-ASCII glyph(s): U+2192 RIGHTWARDS ARROW :: The Grave of Er.→ In the old grave</t>
+        </is>
+      </c>
+      <c r="K32" s="1" t="inlineStr"/>
       <c r="L32" s="1" t="inlineStr"/>
       <c r="M32" s="1" t="inlineStr"/>
       <c r="N32" s="1" t="inlineStr">
         <is>
-          <t>L199: isolated marker/symbol line :: .</t>
+          <t>L185: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O32" s="1" t="inlineStr">
         <is>
-          <t>L576: symbol-only separator/garbage line :: 4 50</t>
+          <t>L566: isolated marker/symbol line :: J.</t>
         </is>
       </c>
       <c r="P32" s="1" t="inlineStr"/>
       <c r="Q32" s="1" t="inlineStr">
         <is>
-          <t>L514: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: double/multiple hyphen :: setting limits to - : --= -----frhis â€” -</t>
+          <t>L514: punctuation artifact: double/multiple hyphen :: setting limits to - : --= -----frhis — -</t>
         </is>
       </c>
       <c r="R32" s="1" t="inlineStr"/>
@@ -2470,24 +2390,20 @@
       <c r="I33" s="1" t="inlineStr"/>
       <c r="J33" s="1" t="inlineStr">
         <is>
-          <t>L1016: stray/suspicious non-ASCII glyph(s): U+00AF MACRON | isolated marker/symbol line :: å¯¿</t>
-        </is>
-      </c>
-      <c r="K33" s="1" t="inlineStr">
-        <is>
-          <t>L586: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Personal.â€”A report is current in</t>
-        </is>
-      </c>
+          <t>L1155: stray/suspicious non-ASCII glyph(s): U+4E1A CJK UNIFIED IDEOGRAPH-4E1A | isolated marker/symbol line :: 业</t>
+        </is>
+      </c>
+      <c r="K33" s="1" t="inlineStr"/>
       <c r="L33" s="1" t="inlineStr"/>
       <c r="M33" s="1" t="inlineStr"/>
       <c r="N33" s="1" t="inlineStr">
         <is>
-          <t>L200: symbol-only separator/garbage line :: 15.6)</t>
+          <t>L187: isolated marker/symbol line :: 400</t>
         </is>
       </c>
       <c r="O33" s="1" t="inlineStr">
         <is>
-          <t>L578: isolated marker/symbol line :: 37</t>
+          <t>L576: symbol-only separator/garbage line :: 4 50</t>
         </is>
       </c>
       <c r="P33" s="1" t="inlineStr"/>
@@ -2517,24 +2433,20 @@
       <c r="I34" s="1" t="inlineStr"/>
       <c r="J34" s="1" t="inlineStr">
         <is>
-          <t>L1018: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: ã€‚</t>
-        </is>
-      </c>
-      <c r="K34" s="1" t="inlineStr">
-        <is>
-          <t>L593: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Englandâ€™s Premier.-Lord Palmerston</t>
-        </is>
-      </c>
+          <t>L1184: stray/suspicious non-ASCII glyph(s): U+81EA CJK UNIFIED IDEOGRAPH-81EA | isolated marker/symbol line :: 自</t>
+        </is>
+      </c>
+      <c r="K34" s="1" t="inlineStr"/>
       <c r="L34" s="1" t="inlineStr"/>
       <c r="M34" s="1" t="inlineStr"/>
       <c r="N34" s="1" t="inlineStr">
         <is>
-          <t>L212: isolated marker/symbol line :: 7</t>
+          <t>L198: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O34" s="1" t="inlineStr">
         <is>
-          <t>L580: isolated marker/symbol line :: 90</t>
+          <t>L578: isolated marker/symbol line :: 37</t>
         </is>
       </c>
       <c r="P34" s="1" t="inlineStr"/>
@@ -2564,24 +2476,20 @@
       <c r="I35" s="1" t="inlineStr"/>
       <c r="J35" s="1" t="inlineStr">
         <is>
-          <t>L1038: stray/suspicious non-ASCII glyph(s): U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: é‡�</t>
-        </is>
-      </c>
-      <c r="K35" s="1" t="inlineStr">
-        <is>
-          <t>L677: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: perhaps $4,800 eachâ€”we suppose paid</t>
-        </is>
-      </c>
+          <t>L1204: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 。</t>
+        </is>
+      </c>
+      <c r="K35" s="1" t="inlineStr"/>
       <c r="L35" s="1" t="inlineStr"/>
       <c r="M35" s="1" t="inlineStr"/>
       <c r="N35" s="1" t="inlineStr">
         <is>
-          <t>L214: symbol-only separator/garbage line :: 8.00</t>
+          <t>L199: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O35" s="1" t="inlineStr">
         <is>
-          <t>L582: symbol-only separator/garbage line :: 1.00</t>
+          <t>L580: isolated marker/symbol line :: 90</t>
         </is>
       </c>
       <c r="P35" s="1" t="inlineStr"/>
@@ -2611,24 +2519,20 @@
       <c r="I36" s="1" t="inlineStr"/>
       <c r="J36" s="1" t="inlineStr">
         <is>
-          <t>L1040: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR, U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: ç¦�</t>
-        </is>
-      </c>
-      <c r="K36" s="1" t="inlineStr">
-        <is>
-          <t>L678: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: quarterly, â€”the one for doing little or</t>
-        </is>
-      </c>
+          <t>L1394: stray/suspicious non-ASCII glyph(s): U+FF1B FULLWIDTH SEMICOLON :: Com easier Mixed 32 ； Yellow 32.</t>
+        </is>
+      </c>
+      <c r="K36" s="1" t="inlineStr"/>
       <c r="L36" s="1" t="inlineStr"/>
       <c r="M36" s="1" t="inlineStr"/>
       <c r="N36" s="1" t="inlineStr">
         <is>
-          <t>L222: symbol-only separator/garbage line :: 5.00</t>
+          <t>L200: symbol-only separator/garbage line :: 15.6)</t>
         </is>
       </c>
       <c r="O36" s="1" t="inlineStr">
         <is>
-          <t>L584: isolated marker/symbol line :: 70</t>
+          <t>L582: symbol-only separator/garbage line :: 1.00</t>
         </is>
       </c>
       <c r="P36" s="1" t="inlineStr"/>
@@ -2658,24 +2562,20 @@
       <c r="I37" s="1" t="inlineStr"/>
       <c r="J37" s="1" t="inlineStr">
         <is>
-          <t>L1103: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: The Solar 000-Eclipse.â€” The path of the</t>
-        </is>
-      </c>
-      <c r="K37" s="1" t="inlineStr">
-        <is>
-          <t>L682: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: What effect the mining excitement down Toronto University.â€”Ed. Wit."</t>
-        </is>
-      </c>
+          <t>L1608: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 。</t>
+        </is>
+      </c>
+      <c r="K37" s="1" t="inlineStr"/>
       <c r="L37" s="1" t="inlineStr"/>
       <c r="M37" s="1" t="inlineStr"/>
       <c r="N37" s="1" t="inlineStr">
         <is>
-          <t>L239: isolated marker/symbol line :: 00</t>
+          <t>L212: isolated marker/symbol line :: 7</t>
         </is>
       </c>
       <c r="O37" s="1" t="inlineStr">
         <is>
-          <t>L625: symbol-only separator/garbage line :: 1.25</t>
+          <t>L584: isolated marker/symbol line :: 70</t>
         </is>
       </c>
       <c r="P37" s="1" t="inlineStr"/>
@@ -2705,24 +2605,20 @@
       <c r="I38" s="1" t="inlineStr"/>
       <c r="J38" s="1" t="inlineStr">
         <is>
-          <t>L1105: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€” Boston Journal.</t>
-        </is>
-      </c>
-      <c r="K38" s="1" t="inlineStr">
-        <is>
-          <t>L706: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: ing down smack on his headâ€”"Pam" Regiments for operations on land. All</t>
-        </is>
-      </c>
+          <t>L1690: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | isolated marker/symbol line :: ©</t>
+        </is>
+      </c>
+      <c r="K38" s="1" t="inlineStr"/>
       <c r="L38" s="1" t="inlineStr"/>
       <c r="M38" s="1" t="inlineStr"/>
       <c r="N38" s="1" t="inlineStr">
         <is>
-          <t>L247: isolated marker/symbol line :: 400</t>
+          <t>L214: symbol-only separator/garbage line :: 8.00</t>
         </is>
       </c>
       <c r="O38" s="1" t="inlineStr">
         <is>
-          <t>L627: symbol-only separator/garbage line :: 7.25</t>
+          <t>L625: symbol-only separator/garbage line :: 1.25</t>
         </is>
       </c>
       <c r="P38" s="1" t="inlineStr"/>
@@ -2752,30 +2648,26 @@
       <c r="I39" s="1" t="inlineStr"/>
       <c r="J39" s="1" t="inlineStr">
         <is>
-          <t>L1155: stray/suspicious non-ASCII glyph(s): U+00B8 CEDILLA :: ä¸š</t>
-        </is>
-      </c>
-      <c r="K39" s="1" t="inlineStr">
-        <is>
-          <t>L737: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Departure of the Japanese.â€” The</t>
-        </is>
-      </c>
+          <t>L1691: stray/suspicious non-ASCII glyph(s): U+53D1 CJK UNIFIED IDEOGRAPH-53D1, U+5143 CJK UNIFIED IDEOGRAPH-5143 :: 发 元</t>
+        </is>
+      </c>
+      <c r="K39" s="1" t="inlineStr"/>
       <c r="L39" s="1" t="inlineStr"/>
       <c r="M39" s="1" t="inlineStr"/>
       <c r="N39" s="1" t="inlineStr">
         <is>
-          <t>L258: isolated marker/symbol line :: 8</t>
+          <t>L222: symbol-only separator/garbage line :: 5.00</t>
         </is>
       </c>
       <c r="O39" s="1" t="inlineStr">
         <is>
-          <t>L628: isolated marker/symbol line :: **</t>
+          <t>L627: symbol-only separator/garbage line :: 7.25</t>
         </is>
       </c>
       <c r="P39" s="1" t="inlineStr"/>
       <c r="Q39" s="1" t="inlineStr">
         <is>
-          <t>L758: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: double/multiple hyphen :: sees the requisite energy and industry ration of friends and foes ; and the sue- affords some slight interpretation ofthe â€”000--------</t>
+          <t>L758: punctuation artifact: double/multiple hyphen :: sees the requisite energy and industry ration of friends and foes ; and the sue- affords some slight interpretation ofthe —000--------</t>
         </is>
       </c>
       <c r="R39" s="1" t="inlineStr"/>
@@ -2799,30 +2691,26 @@
       <c r="I40" s="1" t="inlineStr"/>
       <c r="J40" s="1" t="inlineStr">
         <is>
-          <t>L1204: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: ã€‚</t>
-        </is>
-      </c>
-      <c r="K40" s="1" t="inlineStr">
-        <is>
-          <t>L745: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN | suspicious token(s): NewIPee (odd internal casing) :: General Walker Again.â€”The NewIPee like Lady Palmerstonâ€™s</t>
-        </is>
-      </c>
+          <t>L1714: stray/suspicious non-ASCII glyph(s): U+98DE CJK UNIFIED IDEOGRAPH-98DE | isolated marker/symbol line :: 飞</t>
+        </is>
+      </c>
+      <c r="K40" s="1" t="inlineStr"/>
       <c r="L40" s="1" t="inlineStr"/>
       <c r="M40" s="1" t="inlineStr"/>
       <c r="N40" s="1" t="inlineStr">
         <is>
-          <t>L267: symbol-only separator/garbage line :: 100.00</t>
+          <t>L239: isolated marker/symbol line :: 00</t>
         </is>
       </c>
       <c r="O40" s="1" t="inlineStr">
         <is>
-          <t>L630: symbol-only separator/garbage line :: 2.00</t>
+          <t>L628: isolated marker/symbol line :: **</t>
         </is>
       </c>
       <c r="P40" s="1" t="inlineStr"/>
       <c r="Q40" s="1" t="inlineStr">
         <is>
-          <t>L764: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN | punctuation artifact: repeated periods :: strongâ€™s fire, .............</t>
+          <t>L764: punctuation artifact: repeated periods :: strong’s fire, .............</t>
         </is>
       </c>
       <c r="R40" s="1" t="inlineStr"/>
@@ -2844,26 +2732,18 @@
       <c r="G41" s="1" t="inlineStr"/>
       <c r="H41" s="1" t="inlineStr"/>
       <c r="I41" s="1" t="inlineStr"/>
-      <c r="J41" s="1" t="inlineStr">
-        <is>
-          <t>L1209: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Personal â€” A mpon is current in</t>
-        </is>
-      </c>
-      <c r="K41" s="1" t="inlineStr">
-        <is>
-          <t>L746: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER :: Clem y eyed man of destiny,â€�leftdresses ? Because they are muzzling</t>
-        </is>
-      </c>
+      <c r="J41" s="1" t="inlineStr"/>
+      <c r="K41" s="1" t="inlineStr"/>
       <c r="L41" s="1" t="inlineStr"/>
       <c r="M41" s="1" t="inlineStr"/>
       <c r="N41" s="1" t="inlineStr">
         <is>
-          <t>L279: symbol-only separator/garbage line :: 94.00</t>
+          <t>L247: isolated marker/symbol line :: 400</t>
         </is>
       </c>
       <c r="O41" s="1" t="inlineStr">
         <is>
-          <t>L632: isolated marker/symbol line :: P</t>
+          <t>L630: symbol-only separator/garbage line :: 2.00</t>
         </is>
       </c>
       <c r="P41" s="1" t="inlineStr"/>
@@ -2891,26 +2771,18 @@
       <c r="G42" s="1" t="inlineStr"/>
       <c r="H42" s="1" t="inlineStr"/>
       <c r="I42" s="1" t="inlineStr"/>
-      <c r="J42" s="1" t="inlineStr">
-        <is>
-          <t>L1317: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Departure of the Japanese.â€” The</t>
-        </is>
-      </c>
-      <c r="K42" s="1" t="inlineStr">
-        <is>
-          <t>L758: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: double/multiple hyphen :: sees the requisite energy and industry ration of friends and foes ; and the sue- affords some slight interpretation ofthe â€”000--------</t>
-        </is>
-      </c>
+      <c r="J42" s="1" t="inlineStr"/>
+      <c r="K42" s="1" t="inlineStr"/>
       <c r="L42" s="1" t="inlineStr"/>
       <c r="M42" s="1" t="inlineStr"/>
       <c r="N42" s="1" t="inlineStr">
         <is>
-          <t>L305: symbol-only separator/garbage line :: 4.05</t>
+          <t>L258: isolated marker/symbol line :: 8</t>
         </is>
       </c>
       <c r="O42" s="1" t="inlineStr">
         <is>
-          <t>L641: isolated marker/symbol line :: 000</t>
+          <t>L632: isolated marker/symbol line :: P</t>
         </is>
       </c>
       <c r="P42" s="1" t="inlineStr"/>
@@ -2938,26 +2810,18 @@
       <c r="G43" s="1" t="inlineStr"/>
       <c r="H43" s="1" t="inlineStr"/>
       <c r="I43" s="1" t="inlineStr"/>
-      <c r="J43" s="1" t="inlineStr">
-        <is>
-          <t>L1320: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: perhaps $4.800 each â€” we suppose paid</t>
-        </is>
-      </c>
-      <c r="K43" s="1" t="inlineStr">
-        <is>
-          <t>L764: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN | punctuation artifact: repeated periods :: strongâ€™s fire, .............</t>
-        </is>
-      </c>
+      <c r="J43" s="1" t="inlineStr"/>
+      <c r="K43" s="1" t="inlineStr"/>
       <c r="L43" s="1" t="inlineStr"/>
       <c r="M43" s="1" t="inlineStr"/>
       <c r="N43" s="1" t="inlineStr">
         <is>
-          <t>L307: isolated marker/symbol line :: u</t>
+          <t>L267: symbol-only separator/garbage line :: 100.00</t>
         </is>
       </c>
       <c r="O43" s="1" t="inlineStr">
         <is>
-          <t>L688: symbol-only separator/garbage line :: 16 00</t>
+          <t>L641: isolated marker/symbol line :: 000</t>
         </is>
       </c>
       <c r="P43" s="1" t="inlineStr"/>
@@ -2985,26 +2849,18 @@
       <c r="G44" s="1" t="inlineStr"/>
       <c r="H44" s="1" t="inlineStr"/>
       <c r="I44" s="1" t="inlineStr"/>
-      <c r="J44" s="1" t="inlineStr">
-        <is>
-          <t>L1375: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Liverpool, Jape 23.â€” Breadstuffs</t>
-        </is>
-      </c>
-      <c r="K44" s="1" t="inlineStr">
-        <is>
-          <t>L803: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Liverpool, June *3. â€” Breadstuffâ€™s</t>
-        </is>
-      </c>
+      <c r="J44" s="1" t="inlineStr"/>
+      <c r="K44" s="1" t="inlineStr"/>
       <c r="L44" s="1" t="inlineStr"/>
       <c r="M44" s="1" t="inlineStr"/>
       <c r="N44" s="1" t="inlineStr">
         <is>
-          <t>L322: isolated marker/symbol line :: 8</t>
+          <t>L279: symbol-only separator/garbage line :: 94.00</t>
         </is>
       </c>
       <c r="O44" s="1" t="inlineStr">
         <is>
-          <t>L690: symbol-only separator/garbage line :: 1.35</t>
+          <t>L688: symbol-only separator/garbage line :: 16 00</t>
         </is>
       </c>
       <c r="P44" s="1" t="inlineStr"/>
@@ -3032,26 +2888,18 @@
       <c r="G45" s="1" t="inlineStr"/>
       <c r="H45" s="1" t="inlineStr"/>
       <c r="I45" s="1" t="inlineStr"/>
-      <c r="J45" s="1" t="inlineStr">
-        <is>
-          <t>L1425: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Ashes quiet â€” Pots 276 61 to 29 3d;</t>
-        </is>
-      </c>
-      <c r="K45" s="1" t="inlineStr">
-        <is>
-          <t>L813: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Ashes quietâ€”Pots 27s 6d to 29 3d ;</t>
-        </is>
-      </c>
+      <c r="J45" s="1" t="inlineStr"/>
+      <c r="K45" s="1" t="inlineStr"/>
       <c r="L45" s="1" t="inlineStr"/>
       <c r="M45" s="1" t="inlineStr"/>
       <c r="N45" s="1" t="inlineStr">
         <is>
-          <t>L327: isolated marker/symbol line :: ?</t>
+          <t>L292: stray/suspicious non-ASCII glyph(s): U+4E1A CJK UNIFIED IDEOGRAPH-4E1A | isolated marker/symbol line :: 业</t>
         </is>
       </c>
       <c r="O45" s="1" t="inlineStr">
         <is>
-          <t>L694: isolated marker/symbol line :: F</t>
+          <t>L690: symbol-only separator/garbage line :: 1.35</t>
         </is>
       </c>
       <c r="P45" s="1" t="inlineStr"/>
@@ -3079,26 +2927,18 @@
       <c r="G46" s="1" t="inlineStr"/>
       <c r="H46" s="1" t="inlineStr"/>
       <c r="I46" s="1" t="inlineStr"/>
-      <c r="J46" s="1" t="inlineStr">
-        <is>
-          <t>L1442: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€” London Corres. N. O. Della.</t>
-        </is>
-      </c>
-      <c r="K46" s="1" t="inlineStr">
-        <is>
-          <t>L819: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: London.â€”Money higher and active</t>
-        </is>
-      </c>
+      <c r="J46" s="1" t="inlineStr"/>
+      <c r="K46" s="1" t="inlineStr"/>
       <c r="L46" s="1" t="inlineStr"/>
       <c r="M46" s="1" t="inlineStr"/>
       <c r="N46" s="1" t="inlineStr">
         <is>
-          <t>L333: isolated marker/symbol line :: 2</t>
+          <t>L305: symbol-only separator/garbage line :: 4.05</t>
         </is>
       </c>
       <c r="O46" s="1" t="inlineStr">
         <is>
-          <t>L695: isolated marker/symbol line :: J</t>
+          <t>L694: isolated marker/symbol line :: F</t>
         </is>
       </c>
       <c r="P46" s="1" t="inlineStr"/>
@@ -3126,32 +2966,24 @@
       <c r="G47" s="1" t="inlineStr"/>
       <c r="H47" s="1" t="inlineStr"/>
       <c r="I47" s="1" t="inlineStr"/>
-      <c r="J47" s="1" t="inlineStr">
-        <is>
-          <t>L1491: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: world â€” a system of which any country</t>
-        </is>
-      </c>
-      <c r="K47" s="1" t="inlineStr">
-        <is>
-          <t>L874: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: to turn the wilderness into â€¢ fruitful cess which he has acheived in establish I transferred to the Hondurean Govern</t>
-        </is>
-      </c>
+      <c r="J47" s="1" t="inlineStr"/>
+      <c r="K47" s="1" t="inlineStr"/>
       <c r="L47" s="1" t="inlineStr"/>
       <c r="M47" s="1" t="inlineStr"/>
       <c r="N47" s="1" t="inlineStr">
         <is>
-          <t>L344: symbol-only separator/garbage line :: 1.00</t>
+          <t>L307: isolated marker/symbol line :: u</t>
         </is>
       </c>
       <c r="O47" s="1" t="inlineStr">
         <is>
-          <t>L697: isolated marker/symbol line :: a</t>
+          <t>L695: isolated marker/symbol line :: J</t>
         </is>
       </c>
       <c r="P47" s="1" t="inlineStr"/>
       <c r="Q47" s="1" t="inlineStr">
         <is>
-          <t>L876: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods; quote/punctuation debris :: sible that if mining is carried on with tion one of the most perfect and efficient [General Walker, in connecting himself, â€žâ€”.._._11_T_._.</t>
+          <t>L876: punctuation artifact: repeated periods :: sible that if mining is carried on with tion one of the most perfect and efficient [General Walker, in connecting himself, „—.._._11_T_._.</t>
         </is>
       </c>
       <c r="R47" s="1" t="inlineStr"/>
@@ -3173,32 +3005,24 @@
       <c r="G48" s="1" t="inlineStr"/>
       <c r="H48" s="1" t="inlineStr"/>
       <c r="I48" s="1" t="inlineStr"/>
-      <c r="J48" s="1" t="inlineStr">
-        <is>
-          <t>L1592: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: about which there is no doubt â€” to</t>
-        </is>
-      </c>
-      <c r="K48" s="1" t="inlineStr">
-        <is>
-          <t>L876: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods; quote/punctuation debris :: sible that if mining is carried on with tion one of the most perfect and efficient [General Walker, in connecting himself, â€žâ€”.._._11_T_._.</t>
-        </is>
-      </c>
+      <c r="J48" s="1" t="inlineStr"/>
+      <c r="K48" s="1" t="inlineStr"/>
       <c r="L48" s="1" t="inlineStr"/>
       <c r="M48" s="1" t="inlineStr"/>
       <c r="N48" s="1" t="inlineStr">
         <is>
-          <t>L354: symbol-only separator/garbage line :: - 000</t>
+          <t>L318: stray/suspicious non-ASCII glyph(s): U+81EA CJK UNIFIED IDEOGRAPH-81EA | isolated marker/symbol line :: 自</t>
         </is>
       </c>
       <c r="O48" s="1" t="inlineStr">
         <is>
-          <t>L729: symbol-only separator/garbage line :: 1.00</t>
+          <t>L697: isolated marker/symbol line :: a</t>
         </is>
       </c>
       <c r="P48" s="1" t="inlineStr"/>
       <c r="Q48" s="1" t="inlineStr">
         <is>
-          <t>L878: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods | suspicious token(s): IEastern (odd internal casing) :: _A_____1:-n....______________________: â€”._...IEastern. The docks, says a curres- ment ceapelied a Sardinian merchant.</t>
+          <t>L878: punctuation artifact: repeated periods | suspicious token(s): IEastern (odd internal casing) :: _A_____1:-n....______________________: —._...IEastern. The docks, says a curres- ment ceapelied a Sardinian merchant.</t>
         </is>
       </c>
       <c r="R48" s="1" t="inlineStr"/>
@@ -3220,26 +3044,18 @@
       <c r="G49" s="1" t="inlineStr"/>
       <c r="H49" s="1" t="inlineStr"/>
       <c r="I49" s="1" t="inlineStr"/>
-      <c r="J49" s="1" t="inlineStr">
-        <is>
-          <t>L1608: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: ã€‚</t>
-        </is>
-      </c>
-      <c r="K49" s="1" t="inlineStr">
-        <is>
-          <t>L878: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods | suspicious token(s): IEastern (odd internal casing) :: _A_____1:-n....______________________: â€”._...IEastern. The docks, says a curres- ment ceapelied a Sardinian merchant.</t>
-        </is>
-      </c>
+      <c r="J49" s="1" t="inlineStr"/>
+      <c r="K49" s="1" t="inlineStr"/>
       <c r="L49" s="1" t="inlineStr"/>
       <c r="M49" s="1" t="inlineStr"/>
       <c r="N49" s="1" t="inlineStr">
         <is>
-          <t>L362: isolated marker/symbol line :: *</t>
+          <t>L322: isolated marker/symbol line :: 8</t>
         </is>
       </c>
       <c r="O49" s="1" t="inlineStr">
         <is>
-          <t>L731: symbol-only separator/garbage line :: 2.00</t>
+          <t>L729: symbol-only separator/garbage line :: 1.00</t>
         </is>
       </c>
       <c r="P49" s="1" t="inlineStr"/>
@@ -3267,32 +3083,24 @@
       <c r="G50" s="1" t="inlineStr"/>
       <c r="H50" s="1" t="inlineStr"/>
       <c r="I50" s="1" t="inlineStr"/>
-      <c r="J50" s="1" t="inlineStr">
-        <is>
-          <t>L1690: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | isolated marker/symbol line :: Â©</t>
-        </is>
-      </c>
-      <c r="K50" s="1" t="inlineStr">
-        <is>
-          <t>L881: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: the attention of the public as to lead to worldâ€”a system of which any country tuated as much by an ultimate design of sp stators, the rigging of the ship- the harbou...</t>
-        </is>
-      </c>
+      <c r="J50" s="1" t="inlineStr"/>
+      <c r="K50" s="1" t="inlineStr"/>
       <c r="L50" s="1" t="inlineStr"/>
       <c r="M50" s="1" t="inlineStr"/>
       <c r="N50" s="1" t="inlineStr">
         <is>
-          <t>L374: isolated marker/symbol line :: 1</t>
+          <t>L327: isolated marker/symbol line :: ?</t>
         </is>
       </c>
       <c r="O50" s="1" t="inlineStr">
         <is>
-          <t>L733: symbol-only separator/garbage line :: 5.00</t>
+          <t>L731: symbol-only separator/garbage line :: 2.00</t>
         </is>
       </c>
       <c r="P50" s="1" t="inlineStr"/>
       <c r="Q50" s="1" t="inlineStr">
         <is>
-          <t>L904: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: double/multiple hyphen | suspicious token(s): 1arlin (letter/digit mix) :: ------------|following are the contents : â€” The child, from seven to ten years old, that Newcastle Station of the Grand Trunk Proceedings of the English 1arlin-</t>
+          <t>L904: punctuation artifact: double/multiple hyphen | suspicious token(s): 1arlin (letter/digit mix) :: ------------|following are the contents : — The child, from seven to ten years old, that Newcastle Station of the Grand Trunk Proceedings of the English 1arlin-</t>
         </is>
       </c>
       <c r="R50" s="1" t="inlineStr"/>
@@ -3314,26 +3122,18 @@
       <c r="G51" s="1" t="inlineStr"/>
       <c r="H51" s="1" t="inlineStr"/>
       <c r="I51" s="1" t="inlineStr"/>
-      <c r="J51" s="1" t="inlineStr">
-        <is>
-          <t>L1691: stray/suspicious non-ASCII glyph(s): U+FFFD REPLACEMENT CHARACTER :: å�‘ å…ƒ</t>
-        </is>
-      </c>
-      <c r="K51" s="1" t="inlineStr">
-        <is>
-          <t>L882: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: the neglect of those resources upon might well be proudâ€”has laid Canada Iragua as to punish Guardiola, the pre pingin the vicinity was filled with ad- Revenue the pa...</t>
-        </is>
-      </c>
+      <c r="J51" s="1" t="inlineStr"/>
+      <c r="K51" s="1" t="inlineStr"/>
       <c r="L51" s="1" t="inlineStr"/>
       <c r="M51" s="1" t="inlineStr"/>
       <c r="N51" s="1" t="inlineStr">
         <is>
-          <t>L375: isolated marker/symbol line :: 1</t>
+          <t>L333: isolated marker/symbol line :: 2</t>
         </is>
       </c>
       <c r="O51" s="1" t="inlineStr">
         <is>
-          <t>L735: symbol-only separator/garbage line :: 334.31</t>
+          <t>L733: symbol-only separator/garbage line :: 5.00</t>
         </is>
       </c>
       <c r="P51" s="1" t="inlineStr"/>
@@ -3362,21 +3162,17 @@
       <c r="H52" s="1" t="inlineStr"/>
       <c r="I52" s="1" t="inlineStr"/>
       <c r="J52" s="1" t="inlineStr"/>
-      <c r="K52" s="1" t="inlineStr">
-        <is>
-          <t>L889: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: of no country rests on a sound founda- of his country's chief benefactors. Dr.is an unmitigated despotism, and the an irrevocable stupidity. They leanerdarmy after hav...</t>
-        </is>
-      </c>
+      <c r="K52" s="1" t="inlineStr"/>
       <c r="L52" s="1" t="inlineStr"/>
       <c r="M52" s="1" t="inlineStr"/>
       <c r="N52" s="1" t="inlineStr">
         <is>
-          <t>L384: isolated marker/symbol line :: 3</t>
+          <t>L344: symbol-only separator/garbage line :: 1.00</t>
         </is>
       </c>
       <c r="O52" s="1" t="inlineStr">
         <is>
-          <t>L834: symbol-only separator/garbage line :: 0.25</t>
+          <t>L735: symbol-only separator/garbage line :: 334.31</t>
         </is>
       </c>
       <c r="P52" s="1" t="inlineStr"/>
@@ -3405,21 +3201,17 @@
       <c r="H53" s="1" t="inlineStr"/>
       <c r="I53" s="1" t="inlineStr"/>
       <c r="J53" s="1" t="inlineStr"/>
-      <c r="K53" s="1" t="inlineStr">
-        <is>
-          <t>L895: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN | suspicious token(s): the28th (letter/digit mix) :: are concerned ; but it is the soil,â€” effect upon the base and slanderousingthe freedom of the Bay Islanders she wasnâ€™t Â°uch a big ship after all would commence on...</t>
-        </is>
-      </c>
+      <c r="K53" s="1" t="inlineStr"/>
       <c r="L53" s="1" t="inlineStr"/>
       <c r="M53" s="1" t="inlineStr"/>
       <c r="N53" s="1" t="inlineStr">
         <is>
-          <t>L395: isolated marker/symbol line :: .</t>
+          <t>L354: symbol-only separator/garbage line :: - 000</t>
         </is>
       </c>
       <c r="O53" s="1" t="inlineStr">
         <is>
-          <t>L835: isolated marker/symbol line :: $</t>
+          <t>L834: symbol-only separator/garbage line :: 0.25</t>
         </is>
       </c>
       <c r="P53" s="1" t="inlineStr"/>
@@ -3448,27 +3240,23 @@
       <c r="H54" s="1" t="inlineStr"/>
       <c r="I54" s="1" t="inlineStr"/>
       <c r="J54" s="1" t="inlineStr"/>
-      <c r="K54" s="1" t="inlineStr">
-        <is>
-          <t>L902: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: ^=^ he see an extensive Blackwoodâ€™s Magazine-The Juwecommand. â€” Robbing a Tracer -On Saterday of Baltimore." The Aperigan Minister</t>
-        </is>
-      </c>
+      <c r="K54" s="1" t="inlineStr"/>
       <c r="L54" s="1" t="inlineStr"/>
       <c r="M54" s="1" t="inlineStr"/>
       <c r="N54" s="1" t="inlineStr">
         <is>
-          <t>L396: symbol-only separator/garbage line :: 2.00</t>
+          <t>L362: isolated marker/symbol line :: *</t>
         </is>
       </c>
       <c r="O54" s="1" t="inlineStr">
         <is>
-          <t>L845: isolated marker/symbol line :: E-</t>
+          <t>L835: isolated marker/symbol line :: $</t>
         </is>
       </c>
       <c r="P54" s="1" t="inlineStr"/>
       <c r="Q54" s="1" t="inlineStr">
         <is>
-          <t>L918: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods :: Mr. I ouis Lampron ...........â€” 4,511</t>
+          <t>L918: punctuation artifact: repeated periods :: Mr. I ouis Lampron ...........— 4,511</t>
         </is>
       </c>
       <c r="R54" s="1" t="inlineStr"/>
@@ -3491,21 +3279,17 @@
       <c r="H55" s="1" t="inlineStr"/>
       <c r="I55" s="1" t="inlineStr"/>
       <c r="J55" s="1" t="inlineStr"/>
-      <c r="K55" s="1" t="inlineStr">
-        <is>
-          <t>L904: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: double/multiple hyphen | suspicious token(s): 1arlin (letter/digit mix) :: ------------|following are the contents : â€” The child, from seven to ten years old, that Newcastle Station of the Grand Trunk Proceedings of the English 1arlin-</t>
-        </is>
-      </c>
+      <c r="K55" s="1" t="inlineStr"/>
       <c r="L55" s="1" t="inlineStr"/>
       <c r="M55" s="1" t="inlineStr"/>
       <c r="N55" s="1" t="inlineStr">
         <is>
-          <t>L410: symbol-only separator/garbage line :: 1600</t>
+          <t>L374: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="O55" s="1" t="inlineStr">
         <is>
-          <t>L864: isolated marker/symbol line :: .:</t>
+          <t>L845: isolated marker/symbol line :: E-</t>
         </is>
       </c>
       <c r="P55" s="1" t="inlineStr"/>
@@ -3534,21 +3318,17 @@
       <c r="H56" s="1" t="inlineStr"/>
       <c r="I56" s="1" t="inlineStr"/>
       <c r="J56" s="1" t="inlineStr"/>
-      <c r="K56" s="1" t="inlineStr">
-        <is>
-          <t>L918: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods :: Mr. I ouis Lampron ...........â€” 4,511</t>
-        </is>
-      </c>
+      <c r="K56" s="1" t="inlineStr"/>
       <c r="L56" s="1" t="inlineStr"/>
       <c r="M56" s="1" t="inlineStr"/>
       <c r="N56" s="1" t="inlineStr">
         <is>
-          <t>L428: isolated marker/symbol line :: 8</t>
+          <t>L375: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="O56" s="1" t="inlineStr">
         <is>
-          <t>L865: symbol-only separator/garbage line :: 5,31</t>
+          <t>L864: isolated marker/symbol line :: .:</t>
         </is>
       </c>
       <c r="P56" s="1" t="inlineStr"/>
@@ -3577,21 +3357,17 @@
       <c r="H57" s="1" t="inlineStr"/>
       <c r="I57" s="1" t="inlineStr"/>
       <c r="J57" s="1" t="inlineStr"/>
-      <c r="K57" s="1" t="inlineStr">
-        <is>
-          <t>L956: stray/suspicious non-ASCII glyph(s): U+00AC NOT SIGN :: Maurice Sayer damage â‚¬</t>
-        </is>
-      </c>
+      <c r="K57" s="1" t="inlineStr"/>
       <c r="L57" s="1" t="inlineStr"/>
       <c r="M57" s="1" t="inlineStr"/>
       <c r="N57" s="1" t="inlineStr">
         <is>
-          <t>L441: isolated marker/symbol line :: 000</t>
+          <t>L384: isolated marker/symbol line :: 3</t>
         </is>
       </c>
       <c r="O57" s="1" t="inlineStr">
         <is>
-          <t>L866: isolated marker/symbol line :: -</t>
+          <t>L865: symbol-only separator/garbage line :: 5,31</t>
         </is>
       </c>
       <c r="P57" s="1" t="inlineStr"/>
@@ -3620,21 +3396,17 @@
       <c r="H58" s="1" t="inlineStr"/>
       <c r="I58" s="1" t="inlineStr"/>
       <c r="J58" s="1" t="inlineStr"/>
-      <c r="K58" s="1" t="inlineStr">
-        <is>
-          <t>L983: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS :: For M. Aaron Hart (RiviÃ¨re du</t>
-        </is>
-      </c>
+      <c r="K58" s="1" t="inlineStr"/>
       <c r="L58" s="1" t="inlineStr"/>
       <c r="M58" s="1" t="inlineStr"/>
       <c r="N58" s="1" t="inlineStr">
         <is>
-          <t>L445: isolated marker/symbol line :: **</t>
+          <t>L395: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O58" s="1" t="inlineStr">
         <is>
-          <t>L867: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ...10,80</t>
+          <t>L866: isolated marker/symbol line :: -</t>
         </is>
       </c>
       <c r="P58" s="1" t="inlineStr"/>
@@ -3663,21 +3435,17 @@
       <c r="H59" s="1" t="inlineStr"/>
       <c r="I59" s="1" t="inlineStr"/>
       <c r="J59" s="1" t="inlineStr"/>
-      <c r="K59" s="1" t="inlineStr">
-        <is>
-          <t>L990: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods :: - Joseph Duval.â€” ................1,60:</t>
-        </is>
-      </c>
+      <c r="K59" s="1" t="inlineStr"/>
       <c r="L59" s="1" t="inlineStr"/>
       <c r="M59" s="1" t="inlineStr"/>
       <c r="N59" s="1" t="inlineStr">
         <is>
-          <t>L446: symbol-only separator/garbage line :: 1.00</t>
+          <t>L396: symbol-only separator/garbage line :: 2.00</t>
         </is>
       </c>
       <c r="O59" s="1" t="inlineStr">
         <is>
-          <t>L869: symbol-only separator/garbage line :: 5,00</t>
+          <t>L867: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ...10,80</t>
         </is>
       </c>
       <c r="P59" s="1" t="inlineStr"/>
@@ -3706,21 +3474,17 @@
       <c r="H60" s="1" t="inlineStr"/>
       <c r="I60" s="1" t="inlineStr"/>
       <c r="J60" s="1" t="inlineStr"/>
-      <c r="K60" s="1" t="inlineStr">
-        <is>
-          <t>L995: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Antoine DÃ©lorier 4 do. 24,00</t>
-        </is>
-      </c>
+      <c r="K60" s="1" t="inlineStr"/>
       <c r="L60" s="1" t="inlineStr"/>
       <c r="M60" s="1" t="inlineStr"/>
       <c r="N60" s="1" t="inlineStr">
         <is>
-          <t>L466: symbol-only separator/garbage line :: 5.00</t>
+          <t>L410: symbol-only separator/garbage line :: 1600</t>
         </is>
       </c>
       <c r="O60" s="1" t="inlineStr">
         <is>
-          <t>L870: symbol-only separator/garbage line | localized OCR phrase divergence vs other OCR: "" vs "750 20 00 a8 08" :: .... 750</t>
+          <t>L869: symbol-only separator/garbage line :: 5,00</t>
         </is>
       </c>
       <c r="P60" s="1" t="inlineStr"/>
@@ -3749,21 +3513,17 @@
       <c r="H61" s="1" t="inlineStr"/>
       <c r="I61" s="1" t="inlineStr"/>
       <c r="J61" s="1" t="inlineStr"/>
-      <c r="K61" s="1" t="inlineStr">
-        <is>
-          <t>L1005: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: The extent end richness of the mine of clair.â€”Part V. Scottish National Cha"</t>
-        </is>
-      </c>
+      <c r="K61" s="1" t="inlineStr"/>
       <c r="L61" s="1" t="inlineStr"/>
       <c r="M61" s="1" t="inlineStr"/>
       <c r="N61" s="1" t="inlineStr">
         <is>
-          <t>L477: symbol-only separator/garbage line :: 30131</t>
+          <t>L428: isolated marker/symbol line :: 8</t>
         </is>
       </c>
       <c r="O61" s="1" t="inlineStr">
         <is>
-          <t>L871: symbol-only separator/garbage line | punctuation artifact: repeated periods :: .... 20,00</t>
+          <t>L870: symbol-only separator/garbage line | localized OCR phrase divergence vs other OCR: "" vs "750 20 00 a8 08" :: .... 750</t>
         </is>
       </c>
       <c r="P61" s="1" t="inlineStr"/>
@@ -3792,21 +3552,17 @@
       <c r="H62" s="1" t="inlineStr"/>
       <c r="I62" s="1" t="inlineStr"/>
       <c r="J62" s="1" t="inlineStr"/>
-      <c r="K62" s="1" t="inlineStr">
-        <is>
-          <t>L1009: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: are not it is true very rich, but they Party.â€¢</t>
-        </is>
-      </c>
+      <c r="K62" s="1" t="inlineStr"/>
       <c r="L62" s="1" t="inlineStr"/>
       <c r="M62" s="1" t="inlineStr"/>
       <c r="N62" s="1" t="inlineStr">
         <is>
-          <t>L480: isolated marker/symbol line :: 2</t>
+          <t>L441: isolated marker/symbol line :: 000</t>
         </is>
       </c>
       <c r="O62" s="1" t="inlineStr">
         <is>
-          <t>L907: symbol-only separator/garbage line | punctuation artifact: double/multiple hyphen | line starts with punctuation glued to text :: ---------------_-</t>
+          <t>L871: symbol-only separator/garbage line | punctuation artifact: repeated periods :: .... 20,00</t>
         </is>
       </c>
       <c r="P62" s="1" t="inlineStr"/>
@@ -3835,21 +3591,17 @@
       <c r="H63" s="1" t="inlineStr"/>
       <c r="I63" s="1" t="inlineStr"/>
       <c r="J63" s="1" t="inlineStr"/>
-      <c r="K63" s="1" t="inlineStr">
-        <is>
-          <t>L1013: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN | punctuation artifact: quote/punctuation debris :: from Peterboroâ€™, and mysteriously dis-steamerleft.,â€”., .â€ž</t>
-        </is>
-      </c>
+      <c r="K63" s="1" t="inlineStr"/>
       <c r="L63" s="1" t="inlineStr"/>
       <c r="M63" s="1" t="inlineStr"/>
       <c r="N63" s="1" t="inlineStr">
         <is>
-          <t>L490: isolated marker/symbol line :: 000</t>
+          <t>L445: isolated marker/symbol line :: **</t>
         </is>
       </c>
       <c r="O63" s="1" t="inlineStr">
         <is>
-          <t>L929: symbol-only separator/garbage line :: $116,374</t>
+          <t>L907: symbol-only separator/garbage line | punctuation artifact: double/multiple hyphen | line starts with punctuation glued to text :: ---------------_-</t>
         </is>
       </c>
       <c r="P63" s="1" t="inlineStr"/>
@@ -3878,21 +3630,17 @@
       <c r="H64" s="1" t="inlineStr"/>
       <c r="I64" s="1" t="inlineStr"/>
       <c r="J64" s="1" t="inlineStr"/>
-      <c r="K64" s="1" t="inlineStr">
-        <is>
-          <t>L1026: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+02DC SMALL TILDE :: -â€˜</t>
-        </is>
-      </c>
+      <c r="K64" s="1" t="inlineStr"/>
       <c r="L64" s="1" t="inlineStr"/>
       <c r="M64" s="1" t="inlineStr"/>
       <c r="N64" s="1" t="inlineStr">
         <is>
-          <t>L508: isolated marker/symbol line :: 2</t>
+          <t>L446: symbol-only separator/garbage line :: 1.00</t>
         </is>
       </c>
       <c r="O64" s="1" t="inlineStr">
         <is>
-          <t>L947: symbol-only separator/garbage line :: 1,00</t>
+          <t>L929: symbol-only separator/garbage line :: $116,374</t>
         </is>
       </c>
       <c r="P64" s="1" t="inlineStr"/>
@@ -3926,12 +3674,12 @@
       <c r="M65" s="1" t="inlineStr"/>
       <c r="N65" s="1" t="inlineStr">
         <is>
-          <t>L516: isolated marker/symbol line :: A</t>
+          <t>L466: symbol-only separator/garbage line :: 5.00</t>
         </is>
       </c>
       <c r="O65" s="1" t="inlineStr">
         <is>
-          <t>L949: isolated marker/symbol line :: 1</t>
+          <t>L947: symbol-only separator/garbage line :: 1,00</t>
         </is>
       </c>
       <c r="P65" s="1" t="inlineStr"/>
@@ -3965,12 +3713,12 @@
       <c r="M66" s="1" t="inlineStr"/>
       <c r="N66" s="1" t="inlineStr">
         <is>
-          <t>L527: symbol-only separator/garbage line :: 1.20</t>
+          <t>L477: symbol-only separator/garbage line :: 30131</t>
         </is>
       </c>
       <c r="O66" s="1" t="inlineStr">
         <is>
-          <t>L951: symbol-only separator/garbage line :: 5,1</t>
+          <t>L949: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="P66" s="1" t="inlineStr"/>
@@ -4004,18 +3752,18 @@
       <c r="M67" s="1" t="inlineStr"/>
       <c r="N67" s="1" t="inlineStr">
         <is>
-          <t>L540: symbol-only separator/garbage line :: 3, 00</t>
+          <t>L480: isolated marker/symbol line :: 2</t>
         </is>
       </c>
       <c r="O67" s="1" t="inlineStr">
         <is>
-          <t>L960: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ... 20,00</t>
+          <t>L951: symbol-only separator/garbage line :: 5,1</t>
         </is>
       </c>
       <c r="P67" s="1" t="inlineStr"/>
       <c r="Q67" s="1" t="inlineStr">
         <is>
-          <t>L990: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods :: - Joseph Duval.â€” ................1,60:</t>
+          <t>L990: punctuation artifact: repeated periods :: - Joseph Duval.— ................1,60:</t>
         </is>
       </c>
       <c r="R67" s="1" t="inlineStr"/>
@@ -4043,12 +3791,12 @@
       <c r="M68" s="1" t="inlineStr"/>
       <c r="N68" s="1" t="inlineStr">
         <is>
-          <t>L543: isolated marker/symbol line :: 2</t>
+          <t>L490: isolated marker/symbol line :: 000</t>
         </is>
       </c>
       <c r="O68" s="1" t="inlineStr">
         <is>
-          <t>L961: isolated marker/symbol line :: - #</t>
+          <t>L960: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ... 20,00</t>
         </is>
       </c>
       <c r="P68" s="1" t="inlineStr"/>
@@ -4082,12 +3830,12 @@
       <c r="M69" s="1" t="inlineStr"/>
       <c r="N69" s="1" t="inlineStr">
         <is>
-          <t>L549: isolated marker/symbol line :: 2</t>
+          <t>L508: isolated marker/symbol line :: 2</t>
         </is>
       </c>
       <c r="O69" s="1" t="inlineStr">
         <is>
-          <t>L969: symbol-only separator/garbage line :: 220,00</t>
+          <t>L961: isolated marker/symbol line :: - #</t>
         </is>
       </c>
       <c r="P69" s="1" t="inlineStr"/>
@@ -4121,20 +3869,16 @@
       <c r="M70" s="1" t="inlineStr"/>
       <c r="N70" s="1" t="inlineStr">
         <is>
-          <t>L551: isolated marker/symbol line :: 531</t>
+          <t>L516: isolated marker/symbol line :: A</t>
         </is>
       </c>
       <c r="O70" s="1" t="inlineStr">
         <is>
-          <t>L970: symbol-only separator/garbage line :: 6,00</t>
+          <t>L969: symbol-only separator/garbage line :: 220,00</t>
         </is>
       </c>
       <c r="P70" s="1" t="inlineStr"/>
-      <c r="Q70" s="1" t="inlineStr">
-        <is>
-          <t>L1013: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN | punctuation artifact: quote/punctuation debris :: from Peterboroâ€™, and mysteriously dis-steamerleft.,â€”., .â€ž</t>
-        </is>
-      </c>
+      <c r="Q70" s="1" t="inlineStr"/>
       <c r="R70" s="1" t="inlineStr"/>
       <c r="S70" s="1" t="inlineStr"/>
       <c r="T70" s="1" t="inlineStr"/>
@@ -4160,12 +3904,12 @@
       <c r="M71" s="1" t="inlineStr"/>
       <c r="N71" s="1" t="inlineStr">
         <is>
-          <t>L560: symbol-only separator/garbage line :: 3, 13</t>
+          <t>L527: symbol-only separator/garbage line :: 1.20</t>
         </is>
       </c>
       <c r="O71" s="1" t="inlineStr">
         <is>
-          <t>L999: isolated marker/symbol line :: 0</t>
+          <t>L970: symbol-only separator/garbage line :: 6,00</t>
         </is>
       </c>
       <c r="P71" s="1" t="inlineStr"/>
@@ -4195,12 +3939,12 @@
       <c r="M72" s="1" t="inlineStr"/>
       <c r="N72" s="1" t="inlineStr">
         <is>
-          <t>L571: symbol-only separator/garbage line :: 10.80</t>
+          <t>L540: symbol-only separator/garbage line :: 3, 00</t>
         </is>
       </c>
       <c r="O72" s="1" t="inlineStr">
         <is>
-          <t>L1001: symbol-only separator/garbage line :: 9,16</t>
+          <t>L999: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="P72" s="1" t="inlineStr"/>
@@ -4230,12 +3974,12 @@
       <c r="M73" s="1" t="inlineStr"/>
       <c r="N73" s="1" t="inlineStr">
         <is>
-          <t>L578: isolated marker/symbol line :: 000</t>
+          <t>L543: isolated marker/symbol line :: 2</t>
         </is>
       </c>
       <c r="O73" s="1" t="inlineStr">
         <is>
-          <t>L1022: isolated marker/symbol line :: %</t>
+          <t>L1001: symbol-only separator/garbage line :: 9,16</t>
         </is>
       </c>
       <c r="P73" s="1" t="inlineStr"/>
@@ -4265,12 +4009,12 @@
       <c r="M74" s="1" t="inlineStr"/>
       <c r="N74" s="1" t="inlineStr">
         <is>
-          <t>L581: symbol-only separator/garbage line :: 5.00</t>
+          <t>L549: isolated marker/symbol line :: 2</t>
         </is>
       </c>
       <c r="O74" s="1" t="inlineStr">
         <is>
-          <t>L1024: isolated marker/symbol line :: -</t>
+          <t>L1022: isolated marker/symbol line :: %</t>
         </is>
       </c>
       <c r="P74" s="1" t="inlineStr"/>
@@ -4300,12 +4044,12 @@
       <c r="M75" s="1" t="inlineStr"/>
       <c r="N75" s="1" t="inlineStr">
         <is>
-          <t>L588: isolated marker/symbol line :: 780</t>
+          <t>L551: isolated marker/symbol line :: 531</t>
         </is>
       </c>
       <c r="O75" s="1" t="inlineStr">
         <is>
-          <t>L1028: isolated marker/symbol line :: a</t>
+          <t>L1024: isolated marker/symbol line :: -</t>
         </is>
       </c>
       <c r="P75" s="1" t="inlineStr"/>
@@ -4335,12 +4079,12 @@
       <c r="M76" s="1" t="inlineStr"/>
       <c r="N76" s="1" t="inlineStr">
         <is>
-          <t>L592: isolated marker/symbol line :: D</t>
+          <t>L560: symbol-only separator/garbage line :: 3, 13</t>
         </is>
       </c>
       <c r="O76" s="1" t="inlineStr">
         <is>
-          <t>L1030: isolated marker/symbol line :: ,</t>
+          <t>L1026: isolated marker/symbol line :: -‘</t>
         </is>
       </c>
       <c r="P76" s="1" t="inlineStr"/>
@@ -4370,12 +4114,12 @@
       <c r="M77" s="1" t="inlineStr"/>
       <c r="N77" s="1" t="inlineStr">
         <is>
-          <t>L595: symbol-only separator/garbage line :: 20.00</t>
+          <t>L571: symbol-only separator/garbage line :: 10.80</t>
         </is>
       </c>
       <c r="O77" s="1" t="inlineStr">
         <is>
-          <t>L1032: isolated marker/symbol line :: -1</t>
+          <t>L1028: isolated marker/symbol line :: a</t>
         </is>
       </c>
       <c r="P77" s="1" t="inlineStr"/>
@@ -4405,12 +4149,12 @@
       <c r="M78" s="1" t="inlineStr"/>
       <c r="N78" s="1" t="inlineStr">
         <is>
-          <t>L600: symbol-only separator/garbage line :: 5.60</t>
+          <t>L578: isolated marker/symbol line :: 000</t>
         </is>
       </c>
       <c r="O78" s="1" t="inlineStr">
         <is>
-          <t>L1034: isolated marker/symbol line :: %</t>
+          <t>L1030: isolated marker/symbol line :: ,</t>
         </is>
       </c>
       <c r="P78" s="1" t="inlineStr"/>
@@ -4440,12 +4184,12 @@
       <c r="M79" s="1" t="inlineStr"/>
       <c r="N79" s="1" t="inlineStr">
         <is>
-          <t>L607: symbol-only separator/garbage line :: 2.50</t>
+          <t>L581: symbol-only separator/garbage line :: 5.00</t>
         </is>
       </c>
       <c r="O79" s="1" t="inlineStr">
         <is>
-          <t>L1036: isolated marker/symbol line :: 1</t>
+          <t>L1032: isolated marker/symbol line :: -1</t>
         </is>
       </c>
       <c r="P79" s="1" t="inlineStr"/>
@@ -4475,12 +4219,12 @@
       <c r="M80" s="1" t="inlineStr"/>
       <c r="N80" s="1" t="inlineStr">
         <is>
-          <t>L611: symbol-only separator/garbage line :: 2, 00</t>
+          <t>L588: isolated marker/symbol line :: 780</t>
         </is>
       </c>
       <c r="O80" s="1" t="inlineStr">
         <is>
-          <t>L1038: isolated marker/symbol line :: %</t>
+          <t>L1034: isolated marker/symbol line :: %</t>
         </is>
       </c>
       <c r="P80" s="1" t="inlineStr"/>
@@ -4510,12 +4254,12 @@
       <c r="M81" s="1" t="inlineStr"/>
       <c r="N81" s="1" t="inlineStr">
         <is>
-          <t>L619: symbol-only separator/garbage line :: 1.12</t>
+          <t>L592: isolated marker/symbol line :: D</t>
         </is>
       </c>
       <c r="O81" s="1" t="inlineStr">
         <is>
-          <t>L1040: isolated marker/symbol line :: %</t>
+          <t>L1036: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="P81" s="1" t="inlineStr"/>
@@ -4545,10 +4289,14 @@
       <c r="M82" s="1" t="inlineStr"/>
       <c r="N82" s="1" t="inlineStr">
         <is>
-          <t>L626: symbol-only separator/garbage line :: 11.</t>
-        </is>
-      </c>
-      <c r="O82" s="1" t="inlineStr"/>
+          <t>L595: symbol-only separator/garbage line :: 20.00</t>
+        </is>
+      </c>
+      <c r="O82" s="1" t="inlineStr">
+        <is>
+          <t>L1038: isolated marker/symbol line :: %</t>
+        </is>
+      </c>
       <c r="P82" s="1" t="inlineStr"/>
       <c r="Q82" s="1" t="inlineStr"/>
       <c r="R82" s="1" t="inlineStr"/>
@@ -4576,10 +4324,14 @@
       <c r="M83" s="1" t="inlineStr"/>
       <c r="N83" s="1" t="inlineStr">
         <is>
-          <t>L629: symbol-only separator/garbage line :: 4516</t>
-        </is>
-      </c>
-      <c r="O83" s="1" t="inlineStr"/>
+          <t>L600: symbol-only separator/garbage line :: 5.60</t>
+        </is>
+      </c>
+      <c r="O83" s="1" t="inlineStr">
+        <is>
+          <t>L1040: isolated marker/symbol line :: %</t>
+        </is>
+      </c>
       <c r="P83" s="1" t="inlineStr"/>
       <c r="Q83" s="1" t="inlineStr"/>
       <c r="R83" s="1" t="inlineStr"/>
@@ -4607,7 +4359,7 @@
       <c r="M84" s="1" t="inlineStr"/>
       <c r="N84" s="1" t="inlineStr">
         <is>
-          <t>L636: isolated marker/symbol line :: 12</t>
+          <t>L607: symbol-only separator/garbage line :: 2.50</t>
         </is>
       </c>
       <c r="O84" s="1" t="inlineStr"/>
@@ -4638,7 +4390,7 @@
       <c r="M85" s="1" t="inlineStr"/>
       <c r="N85" s="1" t="inlineStr">
         <is>
-          <t>L642: isolated marker/symbol line :: 2</t>
+          <t>L611: symbol-only separator/garbage line :: 2, 00</t>
         </is>
       </c>
       <c r="O85" s="1" t="inlineStr"/>
@@ -4669,7 +4421,7 @@
       <c r="M86" s="1" t="inlineStr"/>
       <c r="N86" s="1" t="inlineStr">
         <is>
-          <t>L643: isolated marker/symbol line :: D</t>
+          <t>L619: symbol-only separator/garbage line :: 1.12</t>
         </is>
       </c>
       <c r="O86" s="1" t="inlineStr"/>
@@ -4700,7 +4452,7 @@
       <c r="M87" s="1" t="inlineStr"/>
       <c r="N87" s="1" t="inlineStr">
         <is>
-          <t>L645: symbol-only separator/garbage line :: 7, 0</t>
+          <t>L626: symbol-only separator/garbage line :: 11.</t>
         </is>
       </c>
       <c r="O87" s="1" t="inlineStr"/>
@@ -4731,7 +4483,7 @@
       <c r="M88" s="1" t="inlineStr"/>
       <c r="N88" s="1" t="inlineStr">
         <is>
-          <t>L653: symbol-only separator/garbage line :: 2, 00</t>
+          <t>L629: symbol-only separator/garbage line :: 4516</t>
         </is>
       </c>
       <c r="O88" s="1" t="inlineStr"/>
@@ -4762,7 +4514,7 @@
       <c r="M89" s="1" t="inlineStr"/>
       <c r="N89" s="1" t="inlineStr">
         <is>
-          <t>L659: symbol-only separator/garbage line :: 6, 60</t>
+          <t>L636: isolated marker/symbol line :: 12</t>
         </is>
       </c>
       <c r="O89" s="1" t="inlineStr"/>
@@ -4793,7 +4545,7 @@
       <c r="M90" s="1" t="inlineStr"/>
       <c r="N90" s="1" t="inlineStr">
         <is>
-          <t>L668: symbol-only separator/garbage line :: $116, 37</t>
+          <t>L642: isolated marker/symbol line :: 2</t>
         </is>
       </c>
       <c r="O90" s="1" t="inlineStr"/>
@@ -4824,7 +4576,7 @@
       <c r="M91" s="1" t="inlineStr"/>
       <c r="N91" s="1" t="inlineStr">
         <is>
-          <t>L688: isolated marker/symbol line :: A</t>
+          <t>L643: isolated marker/symbol line :: D</t>
         </is>
       </c>
       <c r="O91" s="1" t="inlineStr"/>
@@ -4855,7 +4607,7 @@
       <c r="M92" s="1" t="inlineStr"/>
       <c r="N92" s="1" t="inlineStr">
         <is>
-          <t>L689: symbol-only separator/garbage line :: 1, 00</t>
+          <t>L645: symbol-only separator/garbage line :: 7, 0</t>
         </is>
       </c>
       <c r="O92" s="1" t="inlineStr"/>
@@ -4886,7 +4638,7 @@
       <c r="M93" s="1" t="inlineStr"/>
       <c r="N93" s="1" t="inlineStr">
         <is>
-          <t>L705: symbol-only separator/garbage line :: 5, 20</t>
+          <t>L653: symbol-only separator/garbage line :: 2, 00</t>
         </is>
       </c>
       <c r="O93" s="1" t="inlineStr"/>
@@ -4917,7 +4669,7 @@
       <c r="M94" s="1" t="inlineStr"/>
       <c r="N94" s="1" t="inlineStr">
         <is>
-          <t>L720: symbol-only separator/garbage line :: 20, 00</t>
+          <t>L659: symbol-only separator/garbage line :: 6, 60</t>
         </is>
       </c>
       <c r="O94" s="1" t="inlineStr"/>
@@ -4948,7 +4700,7 @@
       <c r="M95" s="1" t="inlineStr"/>
       <c r="N95" s="1" t="inlineStr">
         <is>
-          <t>L731: isolated marker/symbol line :: 7</t>
+          <t>L668: symbol-only separator/garbage line :: $116, 37</t>
         </is>
       </c>
       <c r="O95" s="1" t="inlineStr"/>
@@ -4979,7 +4731,7 @@
       <c r="M96" s="1" t="inlineStr"/>
       <c r="N96" s="1" t="inlineStr">
         <is>
-          <t>L737: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: ã€‚</t>
+          <t>L688: isolated marker/symbol line :: A</t>
         </is>
       </c>
       <c r="O96" s="1" t="inlineStr"/>
@@ -5010,7 +4762,7 @@
       <c r="M97" s="1" t="inlineStr"/>
       <c r="N97" s="1" t="inlineStr">
         <is>
-          <t>L754: isolated marker/symbol line :: 000</t>
+          <t>L689: symbol-only separator/garbage line :: 1, 00</t>
         </is>
       </c>
       <c r="O97" s="1" t="inlineStr"/>
@@ -5041,7 +4793,7 @@
       <c r="M98" s="1" t="inlineStr"/>
       <c r="N98" s="1" t="inlineStr">
         <is>
-          <t>L757: symbol-only separator/garbage line :: 220, 00</t>
+          <t>L705: symbol-only separator/garbage line :: 5, 20</t>
         </is>
       </c>
       <c r="O98" s="1" t="inlineStr"/>
@@ -5072,7 +4824,7 @@
       <c r="M99" s="1" t="inlineStr"/>
       <c r="N99" s="1" t="inlineStr">
         <is>
-          <t>L764: isolated marker/symbol line :: 3</t>
+          <t>L720: symbol-only separator/garbage line :: 20, 00</t>
         </is>
       </c>
       <c r="O99" s="1" t="inlineStr"/>
@@ -5103,7 +4855,7 @@
       <c r="M100" s="1" t="inlineStr"/>
       <c r="N100" s="1" t="inlineStr">
         <is>
-          <t>L771: symbol-only separator/garbage line :: 3.00</t>
+          <t>L731: isolated marker/symbol line :: 7</t>
         </is>
       </c>
       <c r="O100" s="1" t="inlineStr"/>
@@ -5134,7 +4886,7 @@
       <c r="M101" s="1" t="inlineStr"/>
       <c r="N101" s="1" t="inlineStr">
         <is>
-          <t>L777: symbol-only separator/garbage line :: 7.55</t>
+          <t>L737: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 。</t>
         </is>
       </c>
       <c r="O101" s="1" t="inlineStr"/>
@@ -5165,7 +4917,7 @@
       <c r="M102" s="1" t="inlineStr"/>
       <c r="N102" s="1" t="inlineStr">
         <is>
-          <t>L783: symbol-only separator/garbage line :: 50.00</t>
+          <t>L754: isolated marker/symbol line :: 000</t>
         </is>
       </c>
       <c r="O102" s="1" t="inlineStr"/>
@@ -5196,7 +4948,7 @@
       <c r="M103" s="1" t="inlineStr"/>
       <c r="N103" s="1" t="inlineStr">
         <is>
-          <t>L786: symbol-only separator/garbage line :: 9, 16</t>
+          <t>L757: symbol-only separator/garbage line :: 220, 00</t>
         </is>
       </c>
       <c r="O103" s="1" t="inlineStr"/>
@@ -5227,7 +4979,7 @@
       <c r="M104" s="1" t="inlineStr"/>
       <c r="N104" s="1" t="inlineStr">
         <is>
-          <t>L797: isolated marker/symbol line :: 3</t>
+          <t>L764: isolated marker/symbol line :: 3</t>
         </is>
       </c>
       <c r="O104" s="1" t="inlineStr"/>
@@ -5258,7 +5010,7 @@
       <c r="M105" s="1" t="inlineStr"/>
       <c r="N105" s="1" t="inlineStr">
         <is>
-          <t>L808: symbol-only separator/garbage line :: 2.56</t>
+          <t>L771: symbol-only separator/garbage line :: 3.00</t>
         </is>
       </c>
       <c r="O105" s="1" t="inlineStr"/>
@@ -5289,7 +5041,7 @@
       <c r="M106" s="1" t="inlineStr"/>
       <c r="N106" s="1" t="inlineStr">
         <is>
-          <t>L813: symbol-only separator/garbage line :: 1.8</t>
+          <t>L777: symbol-only separator/garbage line :: 7.55</t>
         </is>
       </c>
       <c r="O106" s="1" t="inlineStr"/>
@@ -5320,7 +5072,7 @@
       <c r="M107" s="1" t="inlineStr"/>
       <c r="N107" s="1" t="inlineStr">
         <is>
-          <t>L819: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | isolated marker/symbol line :: Â©</t>
+          <t>L783: symbol-only separator/garbage line :: 50.00</t>
         </is>
       </c>
       <c r="O107" s="1" t="inlineStr"/>
@@ -5351,7 +5103,7 @@
       <c r="M108" s="1" t="inlineStr"/>
       <c r="N108" s="1" t="inlineStr">
         <is>
-          <t>L832: symbol-only separator/garbage line :: 24.00</t>
+          <t>L786: symbol-only separator/garbage line :: 9, 16</t>
         </is>
       </c>
       <c r="O108" s="1" t="inlineStr"/>
@@ -5382,7 +5134,7 @@
       <c r="M109" s="1" t="inlineStr"/>
       <c r="N109" s="1" t="inlineStr">
         <is>
-          <t>L857: symbol-only separator/garbage line :: 383.25</t>
+          <t>L797: isolated marker/symbol line :: 3</t>
         </is>
       </c>
       <c r="O109" s="1" t="inlineStr"/>
@@ -5413,7 +5165,7 @@
       <c r="M110" s="1" t="inlineStr"/>
       <c r="N110" s="1" t="inlineStr">
         <is>
-          <t>L858: symbol-only separator/garbage line :: 58, 66</t>
+          <t>L808: symbol-only separator/garbage line :: 2.56</t>
         </is>
       </c>
       <c r="O110" s="1" t="inlineStr"/>
@@ -5444,7 +5196,7 @@
       <c r="M111" s="1" t="inlineStr"/>
       <c r="N111" s="1" t="inlineStr">
         <is>
-          <t>L866: symbol-only separator/garbage line :: 11.00</t>
+          <t>L813: symbol-only separator/garbage line :: 1.8</t>
         </is>
       </c>
       <c r="O111" s="1" t="inlineStr"/>
@@ -5475,7 +5227,7 @@
       <c r="M112" s="1" t="inlineStr"/>
       <c r="N112" s="1" t="inlineStr">
         <is>
-          <t>L873: symbol-only separator/garbage line :: 7, 00</t>
+          <t>L819: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | isolated marker/symbol line :: ©</t>
         </is>
       </c>
       <c r="O112" s="1" t="inlineStr"/>
@@ -5506,7 +5258,7 @@
       <c r="M113" s="1" t="inlineStr"/>
       <c r="N113" s="1" t="inlineStr">
         <is>
-          <t>L877: isolated marker/symbol line :: y</t>
+          <t>L832: symbol-only separator/garbage line :: 24.00</t>
         </is>
       </c>
       <c r="O113" s="1" t="inlineStr"/>
@@ -5537,7 +5289,7 @@
       <c r="M114" s="1" t="inlineStr"/>
       <c r="N114" s="1" t="inlineStr">
         <is>
-          <t>L881: symbol-only separator/garbage line :: 42.97</t>
+          <t>L842: stray/suspicious non-ASCII glyph(s): U+98DE CJK UNIFIED IDEOGRAPH-98DE | isolated marker/symbol line :: 飞</t>
         </is>
       </c>
       <c r="O114" s="1" t="inlineStr"/>
@@ -5568,7 +5320,7 @@
       <c r="M115" s="1" t="inlineStr"/>
       <c r="N115" s="1" t="inlineStr">
         <is>
-          <t>L882: isolated marker/symbol line :: 1</t>
+          <t>L857: symbol-only separator/garbage line :: 383.25</t>
         </is>
       </c>
       <c r="O115" s="1" t="inlineStr"/>
@@ -5599,7 +5351,7 @@
       <c r="M116" s="1" t="inlineStr"/>
       <c r="N116" s="1" t="inlineStr">
         <is>
-          <t>L885: symbol-only separator/garbage line :: 528, 00</t>
+          <t>L858: symbol-only separator/garbage line :: 58, 66</t>
         </is>
       </c>
       <c r="O116" s="1" t="inlineStr"/>
@@ -5630,7 +5382,7 @@
       <c r="M117" s="1" t="inlineStr"/>
       <c r="N117" s="1" t="inlineStr">
         <is>
-          <t>L891: symbol-only separator/garbage line :: 3.50</t>
+          <t>L866: symbol-only separator/garbage line :: 11.00</t>
         </is>
       </c>
       <c r="O117" s="1" t="inlineStr"/>
@@ -5661,7 +5413,7 @@
       <c r="M118" s="1" t="inlineStr"/>
       <c r="N118" s="1" t="inlineStr">
         <is>
-          <t>L898: symbol-only separator/garbage line :: 60, 00</t>
+          <t>L873: symbol-only separator/garbage line :: 7, 00</t>
         </is>
       </c>
       <c r="O118" s="1" t="inlineStr"/>
@@ -5692,7 +5444,7 @@
       <c r="M119" s="1" t="inlineStr"/>
       <c r="N119" s="1" t="inlineStr">
         <is>
-          <t>L909: symbol-only separator/garbage line :: 892, 00</t>
+          <t>L877: isolated marker/symbol line :: y</t>
         </is>
       </c>
       <c r="O119" s="1" t="inlineStr"/>
@@ -5723,7 +5475,7 @@
       <c r="M120" s="1" t="inlineStr"/>
       <c r="N120" s="1" t="inlineStr">
         <is>
-          <t>L913: isolated marker/symbol line :: 000</t>
+          <t>L881: symbol-only separator/garbage line :: 42.97</t>
         </is>
       </c>
       <c r="O120" s="1" t="inlineStr"/>
@@ -5754,7 +5506,7 @@
       <c r="M121" s="1" t="inlineStr"/>
       <c r="N121" s="1" t="inlineStr">
         <is>
-          <t>L917: symbol-only separator/garbage line :: 1906.30</t>
+          <t>L882: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="O121" s="1" t="inlineStr"/>
@@ -5785,7 +5537,7 @@
       <c r="M122" s="1" t="inlineStr"/>
       <c r="N122" s="1" t="inlineStr">
         <is>
-          <t>L931: symbol-only separator/garbage line :: 637509</t>
+          <t>L885: symbol-only separator/garbage line :: 528, 00</t>
         </is>
       </c>
       <c r="O122" s="1" t="inlineStr"/>
@@ -5816,7 +5568,7 @@
       <c r="M123" s="1" t="inlineStr"/>
       <c r="N123" s="1" t="inlineStr">
         <is>
-          <t>L932: isolated marker/symbol line :: 4</t>
+          <t>L891: symbol-only separator/garbage line :: 3.50</t>
         </is>
       </c>
       <c r="O123" s="1" t="inlineStr"/>
@@ -5847,7 +5599,7 @@
       <c r="M124" s="1" t="inlineStr"/>
       <c r="N124" s="1" t="inlineStr">
         <is>
-          <t>L936: isolated marker/symbol line :: ,</t>
+          <t>L898: symbol-only separator/garbage line :: 60, 00</t>
         </is>
       </c>
       <c r="O124" s="1" t="inlineStr"/>
@@ -5878,7 +5630,7 @@
       <c r="M125" s="1" t="inlineStr"/>
       <c r="N125" s="1" t="inlineStr">
         <is>
-          <t>L944: isolated marker/symbol line :: 0</t>
+          <t>L909: symbol-only separator/garbage line :: 892, 00</t>
         </is>
       </c>
       <c r="O125" s="1" t="inlineStr"/>
@@ -5909,7 +5661,7 @@
       <c r="M126" s="1" t="inlineStr"/>
       <c r="N126" s="1" t="inlineStr">
         <is>
-          <t>L950: isolated marker/symbol line :: 30</t>
+          <t>L913: isolated marker/symbol line :: 000</t>
         </is>
       </c>
       <c r="O126" s="1" t="inlineStr"/>
@@ -5940,7 +5692,7 @@
       <c r="M127" s="1" t="inlineStr"/>
       <c r="N127" s="1" t="inlineStr">
         <is>
-          <t>L951: isolated marker/symbol line :: F</t>
+          <t>L917: symbol-only separator/garbage line :: 1906.30</t>
         </is>
       </c>
       <c r="O127" s="1" t="inlineStr"/>
@@ -5971,7 +5723,7 @@
       <c r="M128" s="1" t="inlineStr"/>
       <c r="N128" s="1" t="inlineStr">
         <is>
-          <t>L959: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR, U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: ç¦�</t>
+          <t>L930: stray/suspicious non-ASCII glyph(s): U+6E90 CJK UNIFIED IDEOGRAPH-6E90 | isolated marker/symbol line :: 源</t>
         </is>
       </c>
       <c r="O128" s="1" t="inlineStr"/>
@@ -6002,7 +5754,7 @@
       <c r="M129" s="1" t="inlineStr"/>
       <c r="N129" s="1" t="inlineStr">
         <is>
-          <t>L966: isolated marker/symbol line :: 70</t>
+          <t>L931: symbol-only separator/garbage line :: 637509</t>
         </is>
       </c>
       <c r="O129" s="1" t="inlineStr"/>
@@ -6033,7 +5785,7 @@
       <c r="M130" s="1" t="inlineStr"/>
       <c r="N130" s="1" t="inlineStr">
         <is>
-          <t>L984: symbol-only separator/garbage line :: 75.00</t>
+          <t>L932: isolated marker/symbol line :: 4</t>
         </is>
       </c>
       <c r="O130" s="1" t="inlineStr"/>
@@ -6064,7 +5816,7 @@
       <c r="M131" s="1" t="inlineStr"/>
       <c r="N131" s="1" t="inlineStr">
         <is>
-          <t>L986: isolated marker/symbol line :: D</t>
+          <t>L936: isolated marker/symbol line :: ,</t>
         </is>
       </c>
       <c r="O131" s="1" t="inlineStr"/>
@@ -6095,7 +5847,7 @@
       <c r="M132" s="1" t="inlineStr"/>
       <c r="N132" s="1" t="inlineStr">
         <is>
-          <t>L993: symbol-only separator/garbage line :: 18.69</t>
+          <t>L943: stray/suspicious non-ASCII glyph(s): U+548C CJK UNIFIED IDEOGRAPH-548C | isolated marker/symbol line :: 和</t>
         </is>
       </c>
       <c r="O132" s="1" t="inlineStr"/>
@@ -6126,7 +5878,7 @@
       <c r="M133" s="1" t="inlineStr"/>
       <c r="N133" s="1" t="inlineStr">
         <is>
-          <t>L999: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR, U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: ç¦�</t>
+          <t>L944: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O133" s="1" t="inlineStr"/>
@@ -6157,7 +5909,7 @@
       <c r="M134" s="1" t="inlineStr"/>
       <c r="N134" s="1" t="inlineStr">
         <is>
-          <t>L1000: isolated marker/symbol line :: æ–°</t>
+          <t>L950: isolated marker/symbol line :: 30</t>
         </is>
       </c>
       <c r="O134" s="1" t="inlineStr"/>
@@ -6188,7 +5940,7 @@
       <c r="M135" s="1" t="inlineStr"/>
       <c r="N135" s="1" t="inlineStr">
         <is>
-          <t>L1002: symbol-only separator/garbage line :: 1.00</t>
+          <t>L951: isolated marker/symbol line :: F</t>
         </is>
       </c>
       <c r="O135" s="1" t="inlineStr"/>
@@ -6219,7 +5971,7 @@
       <c r="M136" s="1" t="inlineStr"/>
       <c r="N136" s="1" t="inlineStr">
         <is>
-          <t>L1016: stray/suspicious non-ASCII glyph(s): U+00AF MACRON | isolated marker/symbol line :: å¯¿</t>
+          <t>L959: stray/suspicious non-ASCII glyph(s): U+798F CJK UNIFIED IDEOGRAPH-798F | isolated marker/symbol line :: 福</t>
         </is>
       </c>
       <c r="O136" s="1" t="inlineStr"/>
@@ -6250,7 +6002,7 @@
       <c r="M137" s="1" t="inlineStr"/>
       <c r="N137" s="1" t="inlineStr">
         <is>
-          <t>L1018: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: ã€‚</t>
+          <t>L966: isolated marker/symbol line :: 70</t>
         </is>
       </c>
       <c r="O137" s="1" t="inlineStr"/>
@@ -6281,7 +6033,7 @@
       <c r="M138" s="1" t="inlineStr"/>
       <c r="N138" s="1" t="inlineStr">
         <is>
-          <t>L1029: symbol-only separator/garbage line :: 10.00</t>
+          <t>L984: symbol-only separator/garbage line :: 75.00</t>
         </is>
       </c>
       <c r="O138" s="1" t="inlineStr"/>
@@ -6312,7 +6064,7 @@
       <c r="M139" s="1" t="inlineStr"/>
       <c r="N139" s="1" t="inlineStr">
         <is>
-          <t>L1038: stray/suspicious non-ASCII glyph(s): U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: é‡�</t>
+          <t>L986: isolated marker/symbol line :: D</t>
         </is>
       </c>
       <c r="O139" s="1" t="inlineStr"/>
@@ -6343,7 +6095,7 @@
       <c r="M140" s="1" t="inlineStr"/>
       <c r="N140" s="1" t="inlineStr">
         <is>
-          <t>L1039: isolated marker/symbol line :: 800</t>
+          <t>L993: symbol-only separator/garbage line :: 18.69</t>
         </is>
       </c>
       <c r="O140" s="1" t="inlineStr"/>
@@ -6374,7 +6126,7 @@
       <c r="M141" s="1" t="inlineStr"/>
       <c r="N141" s="1" t="inlineStr">
         <is>
-          <t>L1040: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR, U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: ç¦�</t>
+          <t>L999: stray/suspicious non-ASCII glyph(s): U+798F CJK UNIFIED IDEOGRAPH-798F | isolated marker/symbol line :: 福</t>
         </is>
       </c>
       <c r="O141" s="1" t="inlineStr"/>
@@ -6405,7 +6157,7 @@
       <c r="M142" s="1" t="inlineStr"/>
       <c r="N142" s="1" t="inlineStr">
         <is>
-          <t>L1045: isolated marker/symbol line :: 0</t>
+          <t>L1000: stray/suspicious non-ASCII glyph(s): U+65B0 CJK UNIFIED IDEOGRAPH-65B0 | isolated marker/symbol line :: 新</t>
         </is>
       </c>
       <c r="O142" s="1" t="inlineStr"/>
@@ -6436,7 +6188,7 @@
       <c r="M143" s="1" t="inlineStr"/>
       <c r="N143" s="1" t="inlineStr">
         <is>
-          <t>L1047: isolated marker/symbol line :: 400</t>
+          <t>L1002: symbol-only separator/garbage line :: 1.00</t>
         </is>
       </c>
       <c r="O143" s="1" t="inlineStr"/>
@@ -6467,7 +6219,7 @@
       <c r="M144" s="1" t="inlineStr"/>
       <c r="N144" s="1" t="inlineStr">
         <is>
-          <t>L1058: isolated marker/symbol line :: .</t>
+          <t>L1004: stray/suspicious non-ASCII glyph(s): U+FF01 FULLWIDTH EXCLAMATION MARK | isolated marker/symbol line :: ！</t>
         </is>
       </c>
       <c r="O144" s="1" t="inlineStr"/>
@@ -6498,7 +6250,7 @@
       <c r="M145" s="1" t="inlineStr"/>
       <c r="N145" s="1" t="inlineStr">
         <is>
-          <t>L1059: isolated marker/symbol line :: .</t>
+          <t>L1016: stray/suspicious non-ASCII glyph(s): U+5BFF CJK UNIFIED IDEOGRAPH-5BFF | isolated marker/symbol line :: 寿</t>
         </is>
       </c>
       <c r="O145" s="1" t="inlineStr"/>
@@ -6529,7 +6281,7 @@
       <c r="M146" s="1" t="inlineStr"/>
       <c r="N146" s="1" t="inlineStr">
         <is>
-          <t>L1060: symbol-only separator/garbage line :: 15.6)</t>
+          <t>L1018: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 。</t>
         </is>
       </c>
       <c r="O146" s="1" t="inlineStr"/>
@@ -6560,7 +6312,7 @@
       <c r="M147" s="1" t="inlineStr"/>
       <c r="N147" s="1" t="inlineStr">
         <is>
-          <t>L1072: isolated marker/symbol line :: 7</t>
+          <t>L1029: symbol-only separator/garbage line :: 10.00</t>
         </is>
       </c>
       <c r="O147" s="1" t="inlineStr"/>
@@ -6591,7 +6343,7 @@
       <c r="M148" s="1" t="inlineStr"/>
       <c r="N148" s="1" t="inlineStr">
         <is>
-          <t>L1074: symbol-only separator/garbage line :: 8.00</t>
+          <t>L1035: stray/suspicious non-ASCII glyph(s): U+70B9 CJK UNIFIED IDEOGRAPH-70B9 | isolated marker/symbol line :: 点</t>
         </is>
       </c>
       <c r="O148" s="1" t="inlineStr"/>
@@ -6622,7 +6374,7 @@
       <c r="M149" s="1" t="inlineStr"/>
       <c r="N149" s="1" t="inlineStr">
         <is>
-          <t>L1082: symbol-only separator/garbage line :: 5.00</t>
+          <t>L1038: stray/suspicious non-ASCII glyph(s): U+91CD CJK UNIFIED IDEOGRAPH-91CD | isolated marker/symbol line :: 重</t>
         </is>
       </c>
       <c r="O149" s="1" t="inlineStr"/>
@@ -6653,7 +6405,7 @@
       <c r="M150" s="1" t="inlineStr"/>
       <c r="N150" s="1" t="inlineStr">
         <is>
-          <t>L1099: isolated marker/symbol line :: 00</t>
+          <t>L1039: isolated marker/symbol line :: 800</t>
         </is>
       </c>
       <c r="O150" s="1" t="inlineStr"/>
@@ -6684,7 +6436,7 @@
       <c r="M151" s="1" t="inlineStr"/>
       <c r="N151" s="1" t="inlineStr">
         <is>
-          <t>L1107: isolated marker/symbol line :: 400</t>
+          <t>L1040: stray/suspicious non-ASCII glyph(s): U+798F CJK UNIFIED IDEOGRAPH-798F | isolated marker/symbol line :: 福</t>
         </is>
       </c>
       <c r="O151" s="1" t="inlineStr"/>
@@ -6715,7 +6467,7 @@
       <c r="M152" s="1" t="inlineStr"/>
       <c r="N152" s="1" t="inlineStr">
         <is>
-          <t>L1119: isolated marker/symbol line :: 8</t>
+          <t>L1045: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O152" s="1" t="inlineStr"/>
@@ -6746,7 +6498,7 @@
       <c r="M153" s="1" t="inlineStr"/>
       <c r="N153" s="1" t="inlineStr">
         <is>
-          <t>L1128: symbol-only separator/garbage line :: 100.00</t>
+          <t>L1047: isolated marker/symbol line :: 400</t>
         </is>
       </c>
       <c r="O153" s="1" t="inlineStr"/>
@@ -6777,7 +6529,7 @@
       <c r="M154" s="1" t="inlineStr"/>
       <c r="N154" s="1" t="inlineStr">
         <is>
-          <t>L1140: symbol-only separator/garbage line :: 94.00</t>
+          <t>L1058: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O154" s="1" t="inlineStr"/>
@@ -6808,7 +6560,7 @@
       <c r="M155" s="1" t="inlineStr"/>
       <c r="N155" s="1" t="inlineStr">
         <is>
-          <t>L1162: isolated marker/symbol line :: G.</t>
+          <t>L1059: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O155" s="1" t="inlineStr"/>
@@ -6839,7 +6591,7 @@
       <c r="M156" s="1" t="inlineStr"/>
       <c r="N156" s="1" t="inlineStr">
         <is>
-          <t>L1169: symbol-only separator/garbage line :: 4.05</t>
+          <t>L1060: symbol-only separator/garbage line :: 15.6)</t>
         </is>
       </c>
       <c r="O156" s="1" t="inlineStr"/>
@@ -6870,7 +6622,7 @@
       <c r="M157" s="1" t="inlineStr"/>
       <c r="N157" s="1" t="inlineStr">
         <is>
-          <t>L1171: isolated marker/symbol line :: u</t>
+          <t>L1072: isolated marker/symbol line :: 7</t>
         </is>
       </c>
       <c r="O157" s="1" t="inlineStr"/>
@@ -6901,7 +6653,7 @@
       <c r="M158" s="1" t="inlineStr"/>
       <c r="N158" s="1" t="inlineStr">
         <is>
-          <t>L1182: isolated marker/symbol line :: C</t>
+          <t>L1074: symbol-only separator/garbage line :: 8.00</t>
         </is>
       </c>
       <c r="O158" s="1" t="inlineStr"/>
@@ -6932,7 +6684,7 @@
       <c r="M159" s="1" t="inlineStr"/>
       <c r="N159" s="1" t="inlineStr">
         <is>
-          <t>L1188: isolated marker/symbol line :: 8</t>
+          <t>L1082: symbol-only separator/garbage line :: 5.00</t>
         </is>
       </c>
       <c r="O159" s="1" t="inlineStr"/>
@@ -6963,7 +6715,7 @@
       <c r="M160" s="1" t="inlineStr"/>
       <c r="N160" s="1" t="inlineStr">
         <is>
-          <t>L1193: isolated marker/symbol line :: ?</t>
+          <t>L1099: isolated marker/symbol line :: 00</t>
         </is>
       </c>
       <c r="O160" s="1" t="inlineStr"/>
@@ -6994,7 +6746,7 @@
       <c r="M161" s="1" t="inlineStr"/>
       <c r="N161" s="1" t="inlineStr">
         <is>
-          <t>L1199: isolated marker/symbol line :: 2</t>
+          <t>L1107: isolated marker/symbol line :: 400</t>
         </is>
       </c>
       <c r="O161" s="1" t="inlineStr"/>
@@ -7025,7 +6777,7 @@
       <c r="M162" s="1" t="inlineStr"/>
       <c r="N162" s="1" t="inlineStr">
         <is>
-          <t>L1204: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: ã€‚</t>
+          <t>L1119: isolated marker/symbol line :: 8</t>
         </is>
       </c>
       <c r="O162" s="1" t="inlineStr"/>
@@ -7056,7 +6808,7 @@
       <c r="M163" s="1" t="inlineStr"/>
       <c r="N163" s="1" t="inlineStr">
         <is>
-          <t>L1211: symbol-only separator/garbage line :: 1.00</t>
+          <t>L1128: symbol-only separator/garbage line :: 100.00</t>
         </is>
       </c>
       <c r="O163" s="1" t="inlineStr"/>
@@ -7087,7 +6839,7 @@
       <c r="M164" s="1" t="inlineStr"/>
       <c r="N164" s="1" t="inlineStr">
         <is>
-          <t>L1221: symbol-only separator/garbage line :: - 000</t>
+          <t>L1140: symbol-only separator/garbage line :: 94.00</t>
         </is>
       </c>
       <c r="O164" s="1" t="inlineStr"/>
@@ -7118,7 +6870,7 @@
       <c r="M165" s="1" t="inlineStr"/>
       <c r="N165" s="1" t="inlineStr">
         <is>
-          <t>L1229: isolated marker/symbol line :: *</t>
+          <t>L1155: stray/suspicious non-ASCII glyph(s): U+4E1A CJK UNIFIED IDEOGRAPH-4E1A | isolated marker/symbol line :: 业</t>
         </is>
       </c>
       <c r="O165" s="1" t="inlineStr"/>
@@ -7149,7 +6901,7 @@
       <c r="M166" s="1" t="inlineStr"/>
       <c r="N166" s="1" t="inlineStr">
         <is>
-          <t>L1241: isolated marker/symbol line :: 1</t>
+          <t>L1162: isolated marker/symbol line :: G.</t>
         </is>
       </c>
       <c r="O166" s="1" t="inlineStr"/>
@@ -7180,7 +6932,7 @@
       <c r="M167" s="1" t="inlineStr"/>
       <c r="N167" s="1" t="inlineStr">
         <is>
-          <t>L1242: isolated marker/symbol line :: 1</t>
+          <t>L1169: symbol-only separator/garbage line :: 4.05</t>
         </is>
       </c>
       <c r="O167" s="1" t="inlineStr"/>
@@ -7211,7 +6963,7 @@
       <c r="M168" s="1" t="inlineStr"/>
       <c r="N168" s="1" t="inlineStr">
         <is>
-          <t>L1251: isolated marker/symbol line :: 3</t>
+          <t>L1171: isolated marker/symbol line :: u</t>
         </is>
       </c>
       <c r="O168" s="1" t="inlineStr"/>
@@ -7242,7 +6994,7 @@
       <c r="M169" s="1" t="inlineStr"/>
       <c r="N169" s="1" t="inlineStr">
         <is>
-          <t>L1258: isolated marker/symbol line :: P</t>
+          <t>L1182: isolated marker/symbol line :: C</t>
         </is>
       </c>
       <c r="O169" s="1" t="inlineStr"/>
@@ -7273,7 +7025,7 @@
       <c r="M170" s="1" t="inlineStr"/>
       <c r="N170" s="1" t="inlineStr">
         <is>
-          <t>L1264: isolated marker/symbol line :: .</t>
+          <t>L1184: stray/suspicious non-ASCII glyph(s): U+81EA CJK UNIFIED IDEOGRAPH-81EA | isolated marker/symbol line :: 自</t>
         </is>
       </c>
       <c r="O170" s="1" t="inlineStr"/>
@@ -7304,7 +7056,7 @@
       <c r="M171" s="1" t="inlineStr"/>
       <c r="N171" s="1" t="inlineStr">
         <is>
-          <t>L1265: symbol-only separator/garbage line :: 2.00</t>
+          <t>L1188: isolated marker/symbol line :: 8</t>
         </is>
       </c>
       <c r="O171" s="1" t="inlineStr"/>
@@ -7335,7 +7087,7 @@
       <c r="M172" s="1" t="inlineStr"/>
       <c r="N172" s="1" t="inlineStr">
         <is>
-          <t>L1279: symbol-only separator/garbage line :: 1600</t>
+          <t>L1193: isolated marker/symbol line :: ?</t>
         </is>
       </c>
       <c r="O172" s="1" t="inlineStr"/>
@@ -7366,7 +7118,7 @@
       <c r="M173" s="1" t="inlineStr"/>
       <c r="N173" s="1" t="inlineStr">
         <is>
-          <t>L1297: isolated marker/symbol line :: 8</t>
+          <t>L1199: isolated marker/symbol line :: 2</t>
         </is>
       </c>
       <c r="O173" s="1" t="inlineStr"/>
@@ -7397,7 +7149,7 @@
       <c r="M174" s="1" t="inlineStr"/>
       <c r="N174" s="1" t="inlineStr">
         <is>
-          <t>L1310: isolated marker/symbol line :: 000</t>
+          <t>L1204: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 。</t>
         </is>
       </c>
       <c r="O174" s="1" t="inlineStr"/>
@@ -7428,7 +7180,7 @@
       <c r="M175" s="1" t="inlineStr"/>
       <c r="N175" s="1" t="inlineStr">
         <is>
-          <t>L1314: isolated marker/symbol line :: **</t>
+          <t>L1211: symbol-only separator/garbage line :: 1.00</t>
         </is>
       </c>
       <c r="O175" s="1" t="inlineStr"/>
@@ -7459,7 +7211,7 @@
       <c r="M176" s="1" t="inlineStr"/>
       <c r="N176" s="1" t="inlineStr">
         <is>
-          <t>L1315: symbol-only separator/garbage line :: 1.00</t>
+          <t>L1221: symbol-only separator/garbage line :: - 000</t>
         </is>
       </c>
       <c r="O176" s="1" t="inlineStr"/>
@@ -7490,7 +7242,7 @@
       <c r="M177" s="1" t="inlineStr"/>
       <c r="N177" s="1" t="inlineStr">
         <is>
-          <t>L1335: symbol-only separator/garbage line :: 5.00</t>
+          <t>L1229: isolated marker/symbol line :: *</t>
         </is>
       </c>
       <c r="O177" s="1" t="inlineStr"/>
@@ -7521,7 +7273,7 @@
       <c r="M178" s="1" t="inlineStr"/>
       <c r="N178" s="1" t="inlineStr">
         <is>
-          <t>L1346: symbol-only separator/garbage line :: 30131</t>
+          <t>L1241: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="O178" s="1" t="inlineStr"/>
@@ -7552,7 +7304,7 @@
       <c r="M179" s="1" t="inlineStr"/>
       <c r="N179" s="1" t="inlineStr">
         <is>
-          <t>L1349: isolated marker/symbol line :: 2</t>
+          <t>L1242: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="O179" s="1" t="inlineStr"/>
@@ -7583,7 +7335,7 @@
       <c r="M180" s="1" t="inlineStr"/>
       <c r="N180" s="1" t="inlineStr">
         <is>
-          <t>L1359: isolated marker/symbol line :: 000</t>
+          <t>L1251: isolated marker/symbol line :: 3</t>
         </is>
       </c>
       <c r="O180" s="1" t="inlineStr"/>
@@ -7614,7 +7366,7 @@
       <c r="M181" s="1" t="inlineStr"/>
       <c r="N181" s="1" t="inlineStr">
         <is>
-          <t>L1377: isolated marker/symbol line :: 2</t>
+          <t>L1258: isolated marker/symbol line :: P</t>
         </is>
       </c>
       <c r="O181" s="1" t="inlineStr"/>
@@ -7645,7 +7397,7 @@
       <c r="M182" s="1" t="inlineStr"/>
       <c r="N182" s="1" t="inlineStr">
         <is>
-          <t>L1385: isolated marker/symbol line :: A</t>
+          <t>L1264: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O182" s="1" t="inlineStr"/>
@@ -7676,7 +7428,7 @@
       <c r="M183" s="1" t="inlineStr"/>
       <c r="N183" s="1" t="inlineStr">
         <is>
-          <t>L1396: symbol-only separator/garbage line :: 1.20</t>
+          <t>L1265: symbol-only separator/garbage line :: 2.00</t>
         </is>
       </c>
       <c r="O183" s="1" t="inlineStr"/>
@@ -7707,7 +7459,7 @@
       <c r="M184" s="1" t="inlineStr"/>
       <c r="N184" s="1" t="inlineStr">
         <is>
-          <t>L1409: symbol-only separator/garbage line :: 3, 00</t>
+          <t>L1279: symbol-only separator/garbage line :: 1600</t>
         </is>
       </c>
       <c r="O184" s="1" t="inlineStr"/>
@@ -7738,7 +7490,7 @@
       <c r="M185" s="1" t="inlineStr"/>
       <c r="N185" s="1" t="inlineStr">
         <is>
-          <t>L1412: isolated marker/symbol line :: 2</t>
+          <t>L1297: isolated marker/symbol line :: 8</t>
         </is>
       </c>
       <c r="O185" s="1" t="inlineStr"/>
@@ -7769,7 +7521,7 @@
       <c r="M186" s="1" t="inlineStr"/>
       <c r="N186" s="1" t="inlineStr">
         <is>
-          <t>L1418: isolated marker/symbol line :: 2</t>
+          <t>L1310: isolated marker/symbol line :: 000</t>
         </is>
       </c>
       <c r="O186" s="1" t="inlineStr"/>
@@ -7800,7 +7552,7 @@
       <c r="M187" s="1" t="inlineStr"/>
       <c r="N187" s="1" t="inlineStr">
         <is>
-          <t>L1420: isolated marker/symbol line :: 531</t>
+          <t>L1314: isolated marker/symbol line :: **</t>
         </is>
       </c>
       <c r="O187" s="1" t="inlineStr"/>
@@ -7831,7 +7583,7 @@
       <c r="M188" s="1" t="inlineStr"/>
       <c r="N188" s="1" t="inlineStr">
         <is>
-          <t>L1429: symbol-only separator/garbage line :: 3, 13</t>
+          <t>L1315: symbol-only separator/garbage line :: 1.00</t>
         </is>
       </c>
       <c r="O188" s="1" t="inlineStr"/>
@@ -7862,7 +7614,7 @@
       <c r="M189" s="1" t="inlineStr"/>
       <c r="N189" s="1" t="inlineStr">
         <is>
-          <t>L1440: symbol-only separator/garbage line :: 10.80</t>
+          <t>L1335: symbol-only separator/garbage line :: 5.00</t>
         </is>
       </c>
       <c r="O189" s="1" t="inlineStr"/>
@@ -7893,7 +7645,7 @@
       <c r="M190" s="1" t="inlineStr"/>
       <c r="N190" s="1" t="inlineStr">
         <is>
-          <t>L1447: isolated marker/symbol line :: 000</t>
+          <t>L1346: symbol-only separator/garbage line :: 30131</t>
         </is>
       </c>
       <c r="O190" s="1" t="inlineStr"/>
@@ -7924,7 +7676,7 @@
       <c r="M191" s="1" t="inlineStr"/>
       <c r="N191" s="1" t="inlineStr">
         <is>
-          <t>L1450: symbol-only separator/garbage line :: 5.00</t>
+          <t>L1349: isolated marker/symbol line :: 2</t>
         </is>
       </c>
       <c r="O191" s="1" t="inlineStr"/>
@@ -7955,7 +7707,7 @@
       <c r="M192" s="1" t="inlineStr"/>
       <c r="N192" s="1" t="inlineStr">
         <is>
-          <t>L1457: isolated marker/symbol line :: 780</t>
+          <t>L1359: isolated marker/symbol line :: 000</t>
         </is>
       </c>
       <c r="O192" s="1" t="inlineStr"/>
@@ -7986,7 +7738,7 @@
       <c r="M193" s="1" t="inlineStr"/>
       <c r="N193" s="1" t="inlineStr">
         <is>
-          <t>L1461: isolated marker/symbol line :: D</t>
+          <t>L1377: isolated marker/symbol line :: 2</t>
         </is>
       </c>
       <c r="O193" s="1" t="inlineStr"/>
@@ -8017,7 +7769,7 @@
       <c r="M194" s="1" t="inlineStr"/>
       <c r="N194" s="1" t="inlineStr">
         <is>
-          <t>L1464: symbol-only separator/garbage line :: 20.00</t>
+          <t>L1385: isolated marker/symbol line :: A</t>
         </is>
       </c>
       <c r="O194" s="1" t="inlineStr"/>
@@ -8048,7 +7800,7 @@
       <c r="M195" s="1" t="inlineStr"/>
       <c r="N195" s="1" t="inlineStr">
         <is>
-          <t>L1465: isolated marker/symbol line :: 1</t>
+          <t>L1396: symbol-only separator/garbage line :: 1.20</t>
         </is>
       </c>
       <c r="O195" s="1" t="inlineStr"/>
@@ -8079,7 +7831,7 @@
       <c r="M196" s="1" t="inlineStr"/>
       <c r="N196" s="1" t="inlineStr">
         <is>
-          <t>L1470: symbol-only separator/garbage line :: 5.60</t>
+          <t>L1409: symbol-only separator/garbage line :: 3, 00</t>
         </is>
       </c>
       <c r="O196" s="1" t="inlineStr"/>
@@ -8110,7 +7862,7 @@
       <c r="M197" s="1" t="inlineStr"/>
       <c r="N197" s="1" t="inlineStr">
         <is>
-          <t>L1477: symbol-only separator/garbage line :: 2.50</t>
+          <t>L1412: isolated marker/symbol line :: 2</t>
         </is>
       </c>
       <c r="O197" s="1" t="inlineStr"/>
@@ -8141,7 +7893,7 @@
       <c r="M198" s="1" t="inlineStr"/>
       <c r="N198" s="1" t="inlineStr">
         <is>
-          <t>L1481: symbol-only separator/garbage line :: 2, 00</t>
+          <t>L1418: isolated marker/symbol line :: 2</t>
         </is>
       </c>
       <c r="O198" s="1" t="inlineStr"/>
@@ -8172,7 +7924,7 @@
       <c r="M199" s="1" t="inlineStr"/>
       <c r="N199" s="1" t="inlineStr">
         <is>
-          <t>L1489: symbol-only separator/garbage line :: 1.12</t>
+          <t>L1420: isolated marker/symbol line :: 531</t>
         </is>
       </c>
       <c r="O199" s="1" t="inlineStr"/>
@@ -8203,7 +7955,7 @@
       <c r="M200" s="1" t="inlineStr"/>
       <c r="N200" s="1" t="inlineStr">
         <is>
-          <t>L1496: symbol-only separator/garbage line :: 11.</t>
+          <t>L1429: symbol-only separator/garbage line :: 3, 13</t>
         </is>
       </c>
       <c r="O200" s="1" t="inlineStr"/>
@@ -8234,7 +7986,7 @@
       <c r="M201" s="1" t="inlineStr"/>
       <c r="N201" s="1" t="inlineStr">
         <is>
-          <t>L1499: symbol-only separator/garbage line :: 4516</t>
+          <t>L1440: symbol-only separator/garbage line :: 10.80</t>
         </is>
       </c>
       <c r="O201" s="1" t="inlineStr"/>
@@ -8265,7 +8017,7 @@
       <c r="M202" s="1" t="inlineStr"/>
       <c r="N202" s="1" t="inlineStr">
         <is>
-          <t>L1506: isolated marker/symbol line :: 12</t>
+          <t>L1447: isolated marker/symbol line :: 000</t>
         </is>
       </c>
       <c r="O202" s="1" t="inlineStr"/>
@@ -8296,7 +8048,7 @@
       <c r="M203" s="1" t="inlineStr"/>
       <c r="N203" s="1" t="inlineStr">
         <is>
-          <t>L1512: isolated marker/symbol line :: 2</t>
+          <t>L1450: symbol-only separator/garbage line :: 5.00</t>
         </is>
       </c>
       <c r="O203" s="1" t="inlineStr"/>
@@ -8327,7 +8079,7 @@
       <c r="M204" s="1" t="inlineStr"/>
       <c r="N204" s="1" t="inlineStr">
         <is>
-          <t>L1513: isolated marker/symbol line :: D</t>
+          <t>L1457: isolated marker/symbol line :: 780</t>
         </is>
       </c>
       <c r="O204" s="1" t="inlineStr"/>
@@ -8358,7 +8110,7 @@
       <c r="M205" s="1" t="inlineStr"/>
       <c r="N205" s="1" t="inlineStr">
         <is>
-          <t>L1515: symbol-only separator/garbage line :: 7, 0</t>
+          <t>L1461: isolated marker/symbol line :: D</t>
         </is>
       </c>
       <c r="O205" s="1" t="inlineStr"/>
@@ -8389,7 +8141,7 @@
       <c r="M206" s="1" t="inlineStr"/>
       <c r="N206" s="1" t="inlineStr">
         <is>
-          <t>L1523: symbol-only separator/garbage line :: 2, 00</t>
+          <t>L1464: symbol-only separator/garbage line :: 20.00</t>
         </is>
       </c>
       <c r="O206" s="1" t="inlineStr"/>
@@ -8420,7 +8172,7 @@
       <c r="M207" s="1" t="inlineStr"/>
       <c r="N207" s="1" t="inlineStr">
         <is>
-          <t>L1530: symbol-only separator/garbage line :: 6, 60</t>
+          <t>L1465: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="O207" s="1" t="inlineStr"/>
@@ -8451,7 +8203,7 @@
       <c r="M208" s="1" t="inlineStr"/>
       <c r="N208" s="1" t="inlineStr">
         <is>
-          <t>L1539: symbol-only separator/garbage line :: $116, 37</t>
+          <t>L1470: symbol-only separator/garbage line :: 5.60</t>
         </is>
       </c>
       <c r="O208" s="1" t="inlineStr"/>
@@ -8482,7 +8234,7 @@
       <c r="M209" s="1" t="inlineStr"/>
       <c r="N209" s="1" t="inlineStr">
         <is>
-          <t>L1559: isolated marker/symbol line :: A</t>
+          <t>L1477: symbol-only separator/garbage line :: 2.50</t>
         </is>
       </c>
       <c r="O209" s="1" t="inlineStr"/>
@@ -8513,7 +8265,7 @@
       <c r="M210" s="1" t="inlineStr"/>
       <c r="N210" s="1" t="inlineStr">
         <is>
-          <t>L1560: symbol-only separator/garbage line :: 1, 00</t>
+          <t>L1481: symbol-only separator/garbage line :: 2, 00</t>
         </is>
       </c>
       <c r="O210" s="1" t="inlineStr"/>
@@ -8544,7 +8296,7 @@
       <c r="M211" s="1" t="inlineStr"/>
       <c r="N211" s="1" t="inlineStr">
         <is>
-          <t>L1576: symbol-only separator/garbage line :: 5, 20</t>
+          <t>L1489: symbol-only separator/garbage line :: 1.12</t>
         </is>
       </c>
       <c r="O211" s="1" t="inlineStr"/>
@@ -8575,7 +8327,7 @@
       <c r="M212" s="1" t="inlineStr"/>
       <c r="N212" s="1" t="inlineStr">
         <is>
-          <t>L1591: symbol-only separator/garbage line :: 20, 00</t>
+          <t>L1496: symbol-only separator/garbage line :: 11.</t>
         </is>
       </c>
       <c r="O212" s="1" t="inlineStr"/>
@@ -8606,7 +8358,7 @@
       <c r="M213" s="1" t="inlineStr"/>
       <c r="N213" s="1" t="inlineStr">
         <is>
-          <t>L1602: isolated marker/symbol line :: 7</t>
+          <t>L1499: symbol-only separator/garbage line :: 4516</t>
         </is>
       </c>
       <c r="O213" s="1" t="inlineStr"/>
@@ -8637,7 +8389,7 @@
       <c r="M214" s="1" t="inlineStr"/>
       <c r="N214" s="1" t="inlineStr">
         <is>
-          <t>L1608: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: ã€‚</t>
+          <t>L1506: isolated marker/symbol line :: 12</t>
         </is>
       </c>
       <c r="O214" s="1" t="inlineStr"/>
@@ -8668,7 +8420,7 @@
       <c r="M215" s="1" t="inlineStr"/>
       <c r="N215" s="1" t="inlineStr">
         <is>
-          <t>L1625: isolated marker/symbol line :: 000</t>
+          <t>L1512: isolated marker/symbol line :: 2</t>
         </is>
       </c>
       <c r="O215" s="1" t="inlineStr"/>
@@ -8699,7 +8451,7 @@
       <c r="M216" s="1" t="inlineStr"/>
       <c r="N216" s="1" t="inlineStr">
         <is>
-          <t>L1628: symbol-only separator/garbage line :: 220, 00</t>
+          <t>L1513: isolated marker/symbol line :: D</t>
         </is>
       </c>
       <c r="O216" s="1" t="inlineStr"/>
@@ -8730,7 +8482,7 @@
       <c r="M217" s="1" t="inlineStr"/>
       <c r="N217" s="1" t="inlineStr">
         <is>
-          <t>L1635: isolated marker/symbol line :: 3</t>
+          <t>L1515: symbol-only separator/garbage line :: 7, 0</t>
         </is>
       </c>
       <c r="O217" s="1" t="inlineStr"/>
@@ -8761,7 +8513,7 @@
       <c r="M218" s="1" t="inlineStr"/>
       <c r="N218" s="1" t="inlineStr">
         <is>
-          <t>L1642: symbol-only separator/garbage line :: 3.00</t>
+          <t>L1523: symbol-only separator/garbage line :: 2, 00</t>
         </is>
       </c>
       <c r="O218" s="1" t="inlineStr"/>
@@ -8792,7 +8544,7 @@
       <c r="M219" s="1" t="inlineStr"/>
       <c r="N219" s="1" t="inlineStr">
         <is>
-          <t>L1648: symbol-only separator/garbage line :: 7.55</t>
+          <t>L1530: symbol-only separator/garbage line :: 6, 60</t>
         </is>
       </c>
       <c r="O219" s="1" t="inlineStr"/>
@@ -8823,7 +8575,7 @@
       <c r="M220" s="1" t="inlineStr"/>
       <c r="N220" s="1" t="inlineStr">
         <is>
-          <t>L1654: symbol-only separator/garbage line :: 50.00</t>
+          <t>L1539: symbol-only separator/garbage line :: $116, 37</t>
         </is>
       </c>
       <c r="O220" s="1" t="inlineStr"/>
@@ -8854,7 +8606,7 @@
       <c r="M221" s="1" t="inlineStr"/>
       <c r="N221" s="1" t="inlineStr">
         <is>
-          <t>L1657: symbol-only separator/garbage line :: 9, 16</t>
+          <t>L1559: isolated marker/symbol line :: A</t>
         </is>
       </c>
       <c r="O221" s="1" t="inlineStr"/>
@@ -8885,7 +8637,7 @@
       <c r="M222" s="1" t="inlineStr"/>
       <c r="N222" s="1" t="inlineStr">
         <is>
-          <t>L1668: isolated marker/symbol line :: 3</t>
+          <t>L1560: symbol-only separator/garbage line :: 1, 00</t>
         </is>
       </c>
       <c r="O222" s="1" t="inlineStr"/>
@@ -8916,7 +8668,7 @@
       <c r="M223" s="1" t="inlineStr"/>
       <c r="N223" s="1" t="inlineStr">
         <is>
-          <t>L1679: symbol-only separator/garbage line :: 2.56</t>
+          <t>L1576: symbol-only separator/garbage line :: 5, 20</t>
         </is>
       </c>
       <c r="O223" s="1" t="inlineStr"/>
@@ -8947,7 +8699,7 @@
       <c r="M224" s="1" t="inlineStr"/>
       <c r="N224" s="1" t="inlineStr">
         <is>
-          <t>L1684: symbol-only separator/garbage line :: 1.8</t>
+          <t>L1591: symbol-only separator/garbage line :: 20, 00</t>
         </is>
       </c>
       <c r="O224" s="1" t="inlineStr"/>
@@ -8978,7 +8730,7 @@
       <c r="M225" s="1" t="inlineStr"/>
       <c r="N225" s="1" t="inlineStr">
         <is>
-          <t>L1690: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | isolated marker/symbol line :: Â©</t>
+          <t>L1602: isolated marker/symbol line :: 7</t>
         </is>
       </c>
       <c r="O225" s="1" t="inlineStr"/>
@@ -9009,7 +8761,7 @@
       <c r="M226" s="1" t="inlineStr"/>
       <c r="N226" s="1" t="inlineStr">
         <is>
-          <t>L1704: symbol-only separator/garbage line :: 24.00</t>
+          <t>L1608: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 。</t>
         </is>
       </c>
       <c r="O226" s="1" t="inlineStr"/>
@@ -9040,7 +8792,7 @@
       <c r="M227" s="1" t="inlineStr"/>
       <c r="N227" s="1" t="inlineStr">
         <is>
-          <t>L1719: isolated marker/symbol line :: 6</t>
+          <t>L1625: isolated marker/symbol line :: 000</t>
         </is>
       </c>
       <c r="O227" s="1" t="inlineStr"/>
@@ -9071,7 +8823,7 @@
       <c r="M228" s="1" t="inlineStr"/>
       <c r="N228" s="1" t="inlineStr">
         <is>
-          <t>L1720: isolated marker/symbol line :: 6</t>
+          <t>L1628: symbol-only separator/garbage line :: 220, 00</t>
         </is>
       </c>
       <c r="O228" s="1" t="inlineStr"/>
@@ -9086,6 +8838,409 @@
       <c r="X228" s="1" t="inlineStr"/>
       <c r="Y228" s="1" t="inlineStr"/>
     </row>
+    <row r="229">
+      <c r="A229" s="1" t="inlineStr"/>
+      <c r="B229" s="1" t="inlineStr"/>
+      <c r="C229" s="1" t="inlineStr"/>
+      <c r="D229" s="1" t="inlineStr"/>
+      <c r="E229" s="1" t="inlineStr"/>
+      <c r="F229" s="1" t="inlineStr"/>
+      <c r="G229" s="1" t="inlineStr"/>
+      <c r="H229" s="1" t="inlineStr"/>
+      <c r="I229" s="1" t="inlineStr"/>
+      <c r="J229" s="1" t="inlineStr"/>
+      <c r="K229" s="1" t="inlineStr"/>
+      <c r="L229" s="1" t="inlineStr"/>
+      <c r="M229" s="1" t="inlineStr"/>
+      <c r="N229" s="1" t="inlineStr">
+        <is>
+          <t>L1635: isolated marker/symbol line :: 3</t>
+        </is>
+      </c>
+      <c r="O229" s="1" t="inlineStr"/>
+      <c r="P229" s="1" t="inlineStr"/>
+      <c r="Q229" s="1" t="inlineStr"/>
+      <c r="R229" s="1" t="inlineStr"/>
+      <c r="S229" s="1" t="inlineStr"/>
+      <c r="T229" s="1" t="inlineStr"/>
+      <c r="U229" s="1" t="inlineStr"/>
+      <c r="V229" s="1" t="inlineStr"/>
+      <c r="W229" s="1" t="inlineStr"/>
+      <c r="X229" s="1" t="inlineStr"/>
+      <c r="Y229" s="1" t="inlineStr"/>
+    </row>
+    <row r="230">
+      <c r="A230" s="1" t="inlineStr"/>
+      <c r="B230" s="1" t="inlineStr"/>
+      <c r="C230" s="1" t="inlineStr"/>
+      <c r="D230" s="1" t="inlineStr"/>
+      <c r="E230" s="1" t="inlineStr"/>
+      <c r="F230" s="1" t="inlineStr"/>
+      <c r="G230" s="1" t="inlineStr"/>
+      <c r="H230" s="1" t="inlineStr"/>
+      <c r="I230" s="1" t="inlineStr"/>
+      <c r="J230" s="1" t="inlineStr"/>
+      <c r="K230" s="1" t="inlineStr"/>
+      <c r="L230" s="1" t="inlineStr"/>
+      <c r="M230" s="1" t="inlineStr"/>
+      <c r="N230" s="1" t="inlineStr">
+        <is>
+          <t>L1642: symbol-only separator/garbage line :: 3.00</t>
+        </is>
+      </c>
+      <c r="O230" s="1" t="inlineStr"/>
+      <c r="P230" s="1" t="inlineStr"/>
+      <c r="Q230" s="1" t="inlineStr"/>
+      <c r="R230" s="1" t="inlineStr"/>
+      <c r="S230" s="1" t="inlineStr"/>
+      <c r="T230" s="1" t="inlineStr"/>
+      <c r="U230" s="1" t="inlineStr"/>
+      <c r="V230" s="1" t="inlineStr"/>
+      <c r="W230" s="1" t="inlineStr"/>
+      <c r="X230" s="1" t="inlineStr"/>
+      <c r="Y230" s="1" t="inlineStr"/>
+    </row>
+    <row r="231">
+      <c r="A231" s="1" t="inlineStr"/>
+      <c r="B231" s="1" t="inlineStr"/>
+      <c r="C231" s="1" t="inlineStr"/>
+      <c r="D231" s="1" t="inlineStr"/>
+      <c r="E231" s="1" t="inlineStr"/>
+      <c r="F231" s="1" t="inlineStr"/>
+      <c r="G231" s="1" t="inlineStr"/>
+      <c r="H231" s="1" t="inlineStr"/>
+      <c r="I231" s="1" t="inlineStr"/>
+      <c r="J231" s="1" t="inlineStr"/>
+      <c r="K231" s="1" t="inlineStr"/>
+      <c r="L231" s="1" t="inlineStr"/>
+      <c r="M231" s="1" t="inlineStr"/>
+      <c r="N231" s="1" t="inlineStr">
+        <is>
+          <t>L1648: symbol-only separator/garbage line :: 7.55</t>
+        </is>
+      </c>
+      <c r="O231" s="1" t="inlineStr"/>
+      <c r="P231" s="1" t="inlineStr"/>
+      <c r="Q231" s="1" t="inlineStr"/>
+      <c r="R231" s="1" t="inlineStr"/>
+      <c r="S231" s="1" t="inlineStr"/>
+      <c r="T231" s="1" t="inlineStr"/>
+      <c r="U231" s="1" t="inlineStr"/>
+      <c r="V231" s="1" t="inlineStr"/>
+      <c r="W231" s="1" t="inlineStr"/>
+      <c r="X231" s="1" t="inlineStr"/>
+      <c r="Y231" s="1" t="inlineStr"/>
+    </row>
+    <row r="232">
+      <c r="A232" s="1" t="inlineStr"/>
+      <c r="B232" s="1" t="inlineStr"/>
+      <c r="C232" s="1" t="inlineStr"/>
+      <c r="D232" s="1" t="inlineStr"/>
+      <c r="E232" s="1" t="inlineStr"/>
+      <c r="F232" s="1" t="inlineStr"/>
+      <c r="G232" s="1" t="inlineStr"/>
+      <c r="H232" s="1" t="inlineStr"/>
+      <c r="I232" s="1" t="inlineStr"/>
+      <c r="J232" s="1" t="inlineStr"/>
+      <c r="K232" s="1" t="inlineStr"/>
+      <c r="L232" s="1" t="inlineStr"/>
+      <c r="M232" s="1" t="inlineStr"/>
+      <c r="N232" s="1" t="inlineStr">
+        <is>
+          <t>L1654: symbol-only separator/garbage line :: 50.00</t>
+        </is>
+      </c>
+      <c r="O232" s="1" t="inlineStr"/>
+      <c r="P232" s="1" t="inlineStr"/>
+      <c r="Q232" s="1" t="inlineStr"/>
+      <c r="R232" s="1" t="inlineStr"/>
+      <c r="S232" s="1" t="inlineStr"/>
+      <c r="T232" s="1" t="inlineStr"/>
+      <c r="U232" s="1" t="inlineStr"/>
+      <c r="V232" s="1" t="inlineStr"/>
+      <c r="W232" s="1" t="inlineStr"/>
+      <c r="X232" s="1" t="inlineStr"/>
+      <c r="Y232" s="1" t="inlineStr"/>
+    </row>
+    <row r="233">
+      <c r="A233" s="1" t="inlineStr"/>
+      <c r="B233" s="1" t="inlineStr"/>
+      <c r="C233" s="1" t="inlineStr"/>
+      <c r="D233" s="1" t="inlineStr"/>
+      <c r="E233" s="1" t="inlineStr"/>
+      <c r="F233" s="1" t="inlineStr"/>
+      <c r="G233" s="1" t="inlineStr"/>
+      <c r="H233" s="1" t="inlineStr"/>
+      <c r="I233" s="1" t="inlineStr"/>
+      <c r="J233" s="1" t="inlineStr"/>
+      <c r="K233" s="1" t="inlineStr"/>
+      <c r="L233" s="1" t="inlineStr"/>
+      <c r="M233" s="1" t="inlineStr"/>
+      <c r="N233" s="1" t="inlineStr">
+        <is>
+          <t>L1657: symbol-only separator/garbage line :: 9, 16</t>
+        </is>
+      </c>
+      <c r="O233" s="1" t="inlineStr"/>
+      <c r="P233" s="1" t="inlineStr"/>
+      <c r="Q233" s="1" t="inlineStr"/>
+      <c r="R233" s="1" t="inlineStr"/>
+      <c r="S233" s="1" t="inlineStr"/>
+      <c r="T233" s="1" t="inlineStr"/>
+      <c r="U233" s="1" t="inlineStr"/>
+      <c r="V233" s="1" t="inlineStr"/>
+      <c r="W233" s="1" t="inlineStr"/>
+      <c r="X233" s="1" t="inlineStr"/>
+      <c r="Y233" s="1" t="inlineStr"/>
+    </row>
+    <row r="234">
+      <c r="A234" s="1" t="inlineStr"/>
+      <c r="B234" s="1" t="inlineStr"/>
+      <c r="C234" s="1" t="inlineStr"/>
+      <c r="D234" s="1" t="inlineStr"/>
+      <c r="E234" s="1" t="inlineStr"/>
+      <c r="F234" s="1" t="inlineStr"/>
+      <c r="G234" s="1" t="inlineStr"/>
+      <c r="H234" s="1" t="inlineStr"/>
+      <c r="I234" s="1" t="inlineStr"/>
+      <c r="J234" s="1" t="inlineStr"/>
+      <c r="K234" s="1" t="inlineStr"/>
+      <c r="L234" s="1" t="inlineStr"/>
+      <c r="M234" s="1" t="inlineStr"/>
+      <c r="N234" s="1" t="inlineStr">
+        <is>
+          <t>L1668: isolated marker/symbol line :: 3</t>
+        </is>
+      </c>
+      <c r="O234" s="1" t="inlineStr"/>
+      <c r="P234" s="1" t="inlineStr"/>
+      <c r="Q234" s="1" t="inlineStr"/>
+      <c r="R234" s="1" t="inlineStr"/>
+      <c r="S234" s="1" t="inlineStr"/>
+      <c r="T234" s="1" t="inlineStr"/>
+      <c r="U234" s="1" t="inlineStr"/>
+      <c r="V234" s="1" t="inlineStr"/>
+      <c r="W234" s="1" t="inlineStr"/>
+      <c r="X234" s="1" t="inlineStr"/>
+      <c r="Y234" s="1" t="inlineStr"/>
+    </row>
+    <row r="235">
+      <c r="A235" s="1" t="inlineStr"/>
+      <c r="B235" s="1" t="inlineStr"/>
+      <c r="C235" s="1" t="inlineStr"/>
+      <c r="D235" s="1" t="inlineStr"/>
+      <c r="E235" s="1" t="inlineStr"/>
+      <c r="F235" s="1" t="inlineStr"/>
+      <c r="G235" s="1" t="inlineStr"/>
+      <c r="H235" s="1" t="inlineStr"/>
+      <c r="I235" s="1" t="inlineStr"/>
+      <c r="J235" s="1" t="inlineStr"/>
+      <c r="K235" s="1" t="inlineStr"/>
+      <c r="L235" s="1" t="inlineStr"/>
+      <c r="M235" s="1" t="inlineStr"/>
+      <c r="N235" s="1" t="inlineStr">
+        <is>
+          <t>L1679: symbol-only separator/garbage line :: 2.56</t>
+        </is>
+      </c>
+      <c r="O235" s="1" t="inlineStr"/>
+      <c r="P235" s="1" t="inlineStr"/>
+      <c r="Q235" s="1" t="inlineStr"/>
+      <c r="R235" s="1" t="inlineStr"/>
+      <c r="S235" s="1" t="inlineStr"/>
+      <c r="T235" s="1" t="inlineStr"/>
+      <c r="U235" s="1" t="inlineStr"/>
+      <c r="V235" s="1" t="inlineStr"/>
+      <c r="W235" s="1" t="inlineStr"/>
+      <c r="X235" s="1" t="inlineStr"/>
+      <c r="Y235" s="1" t="inlineStr"/>
+    </row>
+    <row r="236">
+      <c r="A236" s="1" t="inlineStr"/>
+      <c r="B236" s="1" t="inlineStr"/>
+      <c r="C236" s="1" t="inlineStr"/>
+      <c r="D236" s="1" t="inlineStr"/>
+      <c r="E236" s="1" t="inlineStr"/>
+      <c r="F236" s="1" t="inlineStr"/>
+      <c r="G236" s="1" t="inlineStr"/>
+      <c r="H236" s="1" t="inlineStr"/>
+      <c r="I236" s="1" t="inlineStr"/>
+      <c r="J236" s="1" t="inlineStr"/>
+      <c r="K236" s="1" t="inlineStr"/>
+      <c r="L236" s="1" t="inlineStr"/>
+      <c r="M236" s="1" t="inlineStr"/>
+      <c r="N236" s="1" t="inlineStr">
+        <is>
+          <t>L1684: symbol-only separator/garbage line :: 1.8</t>
+        </is>
+      </c>
+      <c r="O236" s="1" t="inlineStr"/>
+      <c r="P236" s="1" t="inlineStr"/>
+      <c r="Q236" s="1" t="inlineStr"/>
+      <c r="R236" s="1" t="inlineStr"/>
+      <c r="S236" s="1" t="inlineStr"/>
+      <c r="T236" s="1" t="inlineStr"/>
+      <c r="U236" s="1" t="inlineStr"/>
+      <c r="V236" s="1" t="inlineStr"/>
+      <c r="W236" s="1" t="inlineStr"/>
+      <c r="X236" s="1" t="inlineStr"/>
+      <c r="Y236" s="1" t="inlineStr"/>
+    </row>
+    <row r="237">
+      <c r="A237" s="1" t="inlineStr"/>
+      <c r="B237" s="1" t="inlineStr"/>
+      <c r="C237" s="1" t="inlineStr"/>
+      <c r="D237" s="1" t="inlineStr"/>
+      <c r="E237" s="1" t="inlineStr"/>
+      <c r="F237" s="1" t="inlineStr"/>
+      <c r="G237" s="1" t="inlineStr"/>
+      <c r="H237" s="1" t="inlineStr"/>
+      <c r="I237" s="1" t="inlineStr"/>
+      <c r="J237" s="1" t="inlineStr"/>
+      <c r="K237" s="1" t="inlineStr"/>
+      <c r="L237" s="1" t="inlineStr"/>
+      <c r="M237" s="1" t="inlineStr"/>
+      <c r="N237" s="1" t="inlineStr">
+        <is>
+          <t>L1690: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | isolated marker/symbol line :: ©</t>
+        </is>
+      </c>
+      <c r="O237" s="1" t="inlineStr"/>
+      <c r="P237" s="1" t="inlineStr"/>
+      <c r="Q237" s="1" t="inlineStr"/>
+      <c r="R237" s="1" t="inlineStr"/>
+      <c r="S237" s="1" t="inlineStr"/>
+      <c r="T237" s="1" t="inlineStr"/>
+      <c r="U237" s="1" t="inlineStr"/>
+      <c r="V237" s="1" t="inlineStr"/>
+      <c r="W237" s="1" t="inlineStr"/>
+      <c r="X237" s="1" t="inlineStr"/>
+      <c r="Y237" s="1" t="inlineStr"/>
+    </row>
+    <row r="238">
+      <c r="A238" s="1" t="inlineStr"/>
+      <c r="B238" s="1" t="inlineStr"/>
+      <c r="C238" s="1" t="inlineStr"/>
+      <c r="D238" s="1" t="inlineStr"/>
+      <c r="E238" s="1" t="inlineStr"/>
+      <c r="F238" s="1" t="inlineStr"/>
+      <c r="G238" s="1" t="inlineStr"/>
+      <c r="H238" s="1" t="inlineStr"/>
+      <c r="I238" s="1" t="inlineStr"/>
+      <c r="J238" s="1" t="inlineStr"/>
+      <c r="K238" s="1" t="inlineStr"/>
+      <c r="L238" s="1" t="inlineStr"/>
+      <c r="M238" s="1" t="inlineStr"/>
+      <c r="N238" s="1" t="inlineStr">
+        <is>
+          <t>L1704: symbol-only separator/garbage line :: 24.00</t>
+        </is>
+      </c>
+      <c r="O238" s="1" t="inlineStr"/>
+      <c r="P238" s="1" t="inlineStr"/>
+      <c r="Q238" s="1" t="inlineStr"/>
+      <c r="R238" s="1" t="inlineStr"/>
+      <c r="S238" s="1" t="inlineStr"/>
+      <c r="T238" s="1" t="inlineStr"/>
+      <c r="U238" s="1" t="inlineStr"/>
+      <c r="V238" s="1" t="inlineStr"/>
+      <c r="W238" s="1" t="inlineStr"/>
+      <c r="X238" s="1" t="inlineStr"/>
+      <c r="Y238" s="1" t="inlineStr"/>
+    </row>
+    <row r="239">
+      <c r="A239" s="1" t="inlineStr"/>
+      <c r="B239" s="1" t="inlineStr"/>
+      <c r="C239" s="1" t="inlineStr"/>
+      <c r="D239" s="1" t="inlineStr"/>
+      <c r="E239" s="1" t="inlineStr"/>
+      <c r="F239" s="1" t="inlineStr"/>
+      <c r="G239" s="1" t="inlineStr"/>
+      <c r="H239" s="1" t="inlineStr"/>
+      <c r="I239" s="1" t="inlineStr"/>
+      <c r="J239" s="1" t="inlineStr"/>
+      <c r="K239" s="1" t="inlineStr"/>
+      <c r="L239" s="1" t="inlineStr"/>
+      <c r="M239" s="1" t="inlineStr"/>
+      <c r="N239" s="1" t="inlineStr">
+        <is>
+          <t>L1714: stray/suspicious non-ASCII glyph(s): U+98DE CJK UNIFIED IDEOGRAPH-98DE | isolated marker/symbol line :: 飞</t>
+        </is>
+      </c>
+      <c r="O239" s="1" t="inlineStr"/>
+      <c r="P239" s="1" t="inlineStr"/>
+      <c r="Q239" s="1" t="inlineStr"/>
+      <c r="R239" s="1" t="inlineStr"/>
+      <c r="S239" s="1" t="inlineStr"/>
+      <c r="T239" s="1" t="inlineStr"/>
+      <c r="U239" s="1" t="inlineStr"/>
+      <c r="V239" s="1" t="inlineStr"/>
+      <c r="W239" s="1" t="inlineStr"/>
+      <c r="X239" s="1" t="inlineStr"/>
+      <c r="Y239" s="1" t="inlineStr"/>
+    </row>
+    <row r="240">
+      <c r="A240" s="1" t="inlineStr"/>
+      <c r="B240" s="1" t="inlineStr"/>
+      <c r="C240" s="1" t="inlineStr"/>
+      <c r="D240" s="1" t="inlineStr"/>
+      <c r="E240" s="1" t="inlineStr"/>
+      <c r="F240" s="1" t="inlineStr"/>
+      <c r="G240" s="1" t="inlineStr"/>
+      <c r="H240" s="1" t="inlineStr"/>
+      <c r="I240" s="1" t="inlineStr"/>
+      <c r="J240" s="1" t="inlineStr"/>
+      <c r="K240" s="1" t="inlineStr"/>
+      <c r="L240" s="1" t="inlineStr"/>
+      <c r="M240" s="1" t="inlineStr"/>
+      <c r="N240" s="1" t="inlineStr">
+        <is>
+          <t>L1719: isolated marker/symbol line :: 6</t>
+        </is>
+      </c>
+      <c r="O240" s="1" t="inlineStr"/>
+      <c r="P240" s="1" t="inlineStr"/>
+      <c r="Q240" s="1" t="inlineStr"/>
+      <c r="R240" s="1" t="inlineStr"/>
+      <c r="S240" s="1" t="inlineStr"/>
+      <c r="T240" s="1" t="inlineStr"/>
+      <c r="U240" s="1" t="inlineStr"/>
+      <c r="V240" s="1" t="inlineStr"/>
+      <c r="W240" s="1" t="inlineStr"/>
+      <c r="X240" s="1" t="inlineStr"/>
+      <c r="Y240" s="1" t="inlineStr"/>
+    </row>
+    <row r="241">
+      <c r="A241" s="1" t="inlineStr"/>
+      <c r="B241" s="1" t="inlineStr"/>
+      <c r="C241" s="1" t="inlineStr"/>
+      <c r="D241" s="1" t="inlineStr"/>
+      <c r="E241" s="1" t="inlineStr"/>
+      <c r="F241" s="1" t="inlineStr"/>
+      <c r="G241" s="1" t="inlineStr"/>
+      <c r="H241" s="1" t="inlineStr"/>
+      <c r="I241" s="1" t="inlineStr"/>
+      <c r="J241" s="1" t="inlineStr"/>
+      <c r="K241" s="1" t="inlineStr"/>
+      <c r="L241" s="1" t="inlineStr"/>
+      <c r="M241" s="1" t="inlineStr"/>
+      <c r="N241" s="1" t="inlineStr">
+        <is>
+          <t>L1720: isolated marker/symbol line :: 6</t>
+        </is>
+      </c>
+      <c r="O241" s="1" t="inlineStr"/>
+      <c r="P241" s="1" t="inlineStr"/>
+      <c r="Q241" s="1" t="inlineStr"/>
+      <c r="R241" s="1" t="inlineStr"/>
+      <c r="S241" s="1" t="inlineStr"/>
+      <c r="T241" s="1" t="inlineStr"/>
+      <c r="U241" s="1" t="inlineStr"/>
+      <c r="V241" s="1" t="inlineStr"/>
+      <c r="W241" s="1" t="inlineStr"/>
+      <c r="X241" s="1" t="inlineStr"/>
+      <c r="Y241" s="1" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
